--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>44434</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>44995</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>45057</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>44223</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>44473</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44876</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44238</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45062</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>44169</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>44972</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45649</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44536</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44481</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>44809</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44068</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45013</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>45799</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>45014</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45666</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44512</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44602</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>44546</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44733</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44839</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>45133</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>44995</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>44749</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44803</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44889</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44671</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45077</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44483</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>45183</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>45229</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45814</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45184</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>44995</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>44099</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44599</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44831</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44393</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44419</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44299</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44299</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44824</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>44430</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>44853</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44546</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44553</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44519</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44323</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44090</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44166</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44265</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44223</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44423</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44407</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44512</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44266</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44266</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44468</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44476</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44599</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44628</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44824</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>44467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44602</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44719</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44391</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44417</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44466</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44496</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44480</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44719</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44370</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44102</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44725</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44251</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44619</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44515</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44168</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44426</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44581</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44468</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44169</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44266</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44265</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44299</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44712</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44783</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44783</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44449</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44351</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44783</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44130</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44510</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44264</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44099</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44495</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44701</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44683</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44475</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44550</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44412</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44426</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44182</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44182</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44085</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44571</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44415</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44455</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>44601</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>44455</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44641</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44602</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44706</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44837</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44838</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44607</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44480</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44260</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>44797</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44616</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44832</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44522</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>44725</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>44725</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44411</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44840</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44526</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44062</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44369</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>44531</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44238</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44523</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44581</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44375</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44789</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44827</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44467</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44725</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>44169</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44270</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44266</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44512</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44790</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44463</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44539</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44605</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44439</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44473</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44225</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44824</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45110</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44784</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44603</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44393</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>44768</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44895</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>44847</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45019</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45209</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44466</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44871</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>44797</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>44909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>45160</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44242</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45050</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>45697</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45697</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44434</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45177</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44977</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44488</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45516</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44789</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44319</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44908</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44862</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45016</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45191</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45678</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44963</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44859</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45215</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45677</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45214</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45033</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>45211</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>45057</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>44433</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45231</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>44852</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45414</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>45076</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44837</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44985</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44888</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44974</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44480</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44440</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44945</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44110</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>45154</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45230</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44865</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45366</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44888</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44888</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45205</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45208</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44155</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>44467</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45100</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>44952</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>44140</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45075</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>44147</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>44886</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45667</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44848</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>45457</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>44887</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>45106</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>44830</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44483</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45457</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>44977</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>44855</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44805</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45231</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44789</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>44474</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44789</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45229</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>44068</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45120</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>44934</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44844</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45415</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>44809</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>44825</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45281</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44461</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44460</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45322</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45281</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45214</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44495</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44833</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45281</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45189</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45098</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44957</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45733</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>44957</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>44965</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45697</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45692</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45462</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45461</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45001</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45001</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>44859</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45099</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>44696</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45601</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45345</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44166</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45107</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45595</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45013</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>44406</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>44886</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45694</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45188</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44523</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45142</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45483</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44860</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45470</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44551</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44838</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44483</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44875</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45239</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>45393</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45677</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>44992</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45169</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>44151</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45478</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45475</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44840</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>44858</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>45329</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>44362</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44970</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45672</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45322</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44945</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44628</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45180</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45475</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44099</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45547</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45002</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>44601</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45666</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45097</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45019</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>44602</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>44602</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>45393</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>45483</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45463</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>44112</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44089</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>45518</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45362</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>45698</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>45393</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45076</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45460</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>44089</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45362</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44491</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45152</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45148</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45393</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45393</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44994</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44173</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44335</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44985</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44130</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44130</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45478</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>45517</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45348</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>45348</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44963</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45785</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45105</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44146</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44621</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>45174</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45785</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>45328</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45328</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>45481</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45461</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45786</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>44957</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45153</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45636</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>44130</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>45479</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45547</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44964</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45125</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45108</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44195</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45438</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44596</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44582</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>44551</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>44551</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>44158</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>44139</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>44980</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44659</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44995</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>45461</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44238</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45211</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45517</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>44172</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44623</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45230</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45384</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44964</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>44140</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44602</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45077</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45674</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45590</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>44151</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45165</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44445</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>45798.5558912037</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45344</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45772.63715277778</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>45247</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>44266</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45240</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45214</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>44600</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45463</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45842</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45225</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45223</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45560</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45694.86898148148</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>45692</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45842</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>45762</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45674</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45231</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45799</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>45316</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44797</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44817</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45141</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45141</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44699</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45215</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>45215</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45565</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45196</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>45604</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45761</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44678</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45204</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44643</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44461</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>45230</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>45061</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45001</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45001</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44968</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>45594</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45594</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45001</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44987</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>45194</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45238</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44664</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45666</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44964</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>44712</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>45096</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45041</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45169</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45204</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45852</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>45852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45153</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>45845</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45204</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44795</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45852</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44212</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>45758</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>45758</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>45813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44760</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>44781</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44781</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>45147</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45813</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45163</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45531</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44853</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45189</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45477</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>45726.64574074074</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>44638</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>44060</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>44518</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44817</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>45302</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45322</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44895</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45853</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45822</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>44085</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>44061</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>44442</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>45226</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>45268</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45688</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45098</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44075</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>45477</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45182</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>45845</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>44439</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>44965</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>44519</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45352</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>44840</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>44231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45827</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>45827</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>45870</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45827</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45827</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>44844</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>44823</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>44859</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>44386</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44862</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44074</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45006</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42267,7 +42267,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>44886</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>44888</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45184</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45700</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44099</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45328</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45229</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45833</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43013,7 +43013,7 @@
         <v>44831</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>45547</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>45833</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>44082</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45328.47</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45167</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45026</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>44159</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45478</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43655,7 +43655,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>44776</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>44103</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>44232</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44449</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>44602</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>45016</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>44411</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>44212</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>44250</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>45107</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>44173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>44160</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>44130</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>44142</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>44942</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         <v>44922</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>44790</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45386</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>44905</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>44694</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>44140</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45111</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>44964</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>44995</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>44602</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45006</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>44816</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45245</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45960,7 +45960,7 @@
         <v>44708</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45222</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45075</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45547</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46188,7 +46188,7 @@
         <v>44169</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44957</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>44694</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46483,7 +46483,7 @@
         <v>45268</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46540,7 +46540,7 @@
         <v>45168</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45563</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>44978</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>44858</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44467</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45509</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45386</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>44603</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>44434</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>44995</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>45057</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>44223</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>44473</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44876</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44238</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45062</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>44169</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>44972</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45649</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44536</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44481</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>44809</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44068</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45013</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>45799</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>45014</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45666</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44512</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44602</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>44546</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44733</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44839</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>45133</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>44995</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>44749</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44803</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44889</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44671</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45077</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44483</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>45183</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>45229</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45814</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45184</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>44995</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>44099</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44599</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44831</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44393</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44419</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44299</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44299</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44824</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>44430</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>44853</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44546</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44553</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44519</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44323</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44090</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44166</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44265</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44223</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44423</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44407</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44512</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44266</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44266</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44468</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44476</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44599</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44628</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44824</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>44467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44602</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44719</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44391</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44417</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44466</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44496</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44480</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44719</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44370</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44102</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44725</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44251</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44619</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44515</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44168</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44426</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44581</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44468</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44169</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44266</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44265</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44299</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44712</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44783</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44783</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44449</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44351</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44783</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44130</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44510</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44264</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44099</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44495</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44701</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44683</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44475</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44550</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44412</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44426</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44182</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44182</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44085</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44571</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44415</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44455</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>44601</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>44455</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44641</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44602</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44706</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44837</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44838</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44607</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44480</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44260</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>44797</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44616</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44832</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44522</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>44725</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>44725</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44411</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44840</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44526</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44062</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44369</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>44531</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44238</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44523</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44581</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44375</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44789</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44827</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44467</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44725</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>44169</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44270</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44266</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44512</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44790</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44463</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44539</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44605</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44439</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44473</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44225</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44824</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45110</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44784</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44603</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44393</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>44768</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44895</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>44847</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45019</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45209</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44466</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44871</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>44797</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>44909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>45160</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44242</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45050</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>45697</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45697</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44434</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45177</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44977</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44488</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45516</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44789</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44319</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44908</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44862</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45016</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45191</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45678</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44963</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44859</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45215</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45677</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45214</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45033</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>45211</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>45057</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>44433</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45231</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>44852</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45414</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>45076</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>44837</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44985</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44888</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44974</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44480</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44440</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>44945</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44110</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>45154</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45230</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44865</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45366</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44888</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44888</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45205</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45208</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44155</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>44467</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45100</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>44952</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>44140</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45075</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>44147</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>44886</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45667</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44848</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>45457</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>44887</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>45106</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>44830</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44483</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45457</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>44977</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>44855</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44805</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45231</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44789</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>44474</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44789</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45229</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>44068</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45120</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>44934</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44844</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45415</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>44809</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>44825</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45281</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44461</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44460</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45322</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45281</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45214</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44495</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44833</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45281</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45189</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45098</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44957</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45733</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>44957</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>44965</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45697</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45692</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45462</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45461</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45001</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45001</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>44859</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45099</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>44696</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45601</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45345</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44166</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45107</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45595</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45013</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>44406</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>44886</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45694</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45188</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44523</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45142</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45483</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44860</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45470</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44551</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44838</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44483</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44875</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45239</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>45393</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45677</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>44992</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45169</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>44151</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45478</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45475</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44840</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>44858</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>45329</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>44362</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44970</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45672</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45322</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44945</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44628</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45180</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45475</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44099</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45547</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45002</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>44412</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>44601</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45666</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45097</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45019</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>44602</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>44602</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>45393</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>45483</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45463</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>44112</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44089</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>45518</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45362</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>45698</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>45393</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45076</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45460</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>44089</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45362</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>44491</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45152</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45148</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45393</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45393</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44994</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44173</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44335</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44985</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44130</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44130</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45478</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>45517</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45348</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>45348</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44963</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45785</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45105</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44146</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44621</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>45174</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45785</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>45328</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45328</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>45481</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45461</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45786</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>44957</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45153</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45636</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>44130</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>45479</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45547</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44964</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45125</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45108</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44195</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45438</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44596</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44582</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>44551</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>44551</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>44158</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>44139</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>44980</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44659</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44995</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>45461</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44238</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45211</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45517</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>44172</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44623</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45230</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45384</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44964</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>44140</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44602</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45077</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45674</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45590</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>44151</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45165</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44445</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>45798.5558912037</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45344</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45772.63715277778</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>45247</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>44266</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45240</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45214</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>44600</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45463</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45842</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45225</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45223</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45560</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45694.86898148148</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>45692</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45842</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>45762</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45674</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45231</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45799</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>45316</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44797</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44817</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45141</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45141</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44699</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45215</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>45215</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45565</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45196</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>45604</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45761</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44678</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45204</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44643</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44461</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>45230</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>45061</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45001</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45001</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44968</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>45594</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45594</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45001</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44987</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>45194</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45238</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44664</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45666</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44964</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>44712</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>45096</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45041</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45169</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45204</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45852</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>45852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45153</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>45845</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45204</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44795</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45852</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44212</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>45758</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>45758</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>45813</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44760</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>44781</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44781</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>45147</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45813</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45163</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45531</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44853</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45189</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45477</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>45726.64574074074</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>44638</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>44060</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>44518</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44817</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>45302</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45322</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44895</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45853</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45822</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>44085</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>44061</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>44442</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>45226</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>45268</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45688</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45098</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44075</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>45477</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45182</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>45845</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>44439</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>44965</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>44519</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45352</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>44840</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>44231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45827</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>45827</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>45870</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45827</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45827</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>44844</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>44823</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>44859</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>44386</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44862</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44074</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45006</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42267,7 +42267,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>44886</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>44888</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45184</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45700</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44099</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45328</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45229</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45833</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43013,7 +43013,7 @@
         <v>44831</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>45547</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>45833</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>44082</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45328.47</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45167</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45026</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>44159</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45478</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43655,7 +43655,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>44776</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>44103</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>44232</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44449</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>44602</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>45016</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>44411</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>44212</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>44250</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>45107</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>44173</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>44160</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>44130</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>44142</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>44942</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         <v>44922</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>44790</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45386</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>44905</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>44694</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>44140</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45111</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>44964</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>44995</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>44602</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45006</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>44816</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45245</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45960,7 +45960,7 @@
         <v>44708</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45222</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45075</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45547</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46188,7 +46188,7 @@
         <v>44169</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44957</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>44694</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46483,7 +46483,7 @@
         <v>45268</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46540,7 +46540,7 @@
         <v>45168</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45563</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>44978</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>44858</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44467</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45509</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45386</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>44977</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>44603</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>44995</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>44434</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>45057</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>44223</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>44876</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44238</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45062</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44473</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>44972</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45649</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>44169</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>45799</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>44068</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45099</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45666</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45013</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>45014</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44536</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44809</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44512</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44602</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>44546</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44733</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44839</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45231</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>44889</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45814</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45229</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44671</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45077</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>44995</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44099</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>44483</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45183</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44599</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>45184</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44831</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44995</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45133</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44749</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44803</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44393</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44419</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44299</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44299</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44824</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>44430</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>44853</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44546</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44553</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44519</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44323</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44090</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44166</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44265</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44423</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44407</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44512</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44266</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44266</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44468</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44476</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44599</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44628</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44824</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>44467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44602</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44719</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44391</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44417</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44466</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44496</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44480</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44719</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44370</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44102</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44725</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44468</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44251</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44619</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44168</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44426</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44581</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44169</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44266</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44265</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44299</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44712</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44783</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44783</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44449</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44783</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44351</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44130</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44510</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44264</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44099</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44495</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44701</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44683</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44550</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>44475</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44412</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44426</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44182</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44182</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44085</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44415</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44571</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44455</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>44601</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>44455</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>44607</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44260</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44797</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44725</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44616</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44832</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44411</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44522</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44526</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44369</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44840</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44531</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44062</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44238</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44523</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44375</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44789</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44827</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44467</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44141</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44725</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44169</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44270</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44266</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44512</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44762</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44463</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44790</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44605</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44225</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>44473</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44539</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44439</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44824</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44393</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44641</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44480</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44847</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45070</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44602</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>44706</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44837</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44838</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44859</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44696</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>44797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44242</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>45414</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44166</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45107</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45595</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45697</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45697</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44434</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45177</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45694</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45188</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>44488</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45362</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>44837</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45677</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44789</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45142</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44319</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44551</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45230</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44875</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44888</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44888</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45393</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44992</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45208</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44945</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45100</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44952</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45678</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45547</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45329</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>44362</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>44412</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45666</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44859</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45215</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>45322</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>44628</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45180</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45002</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>44601</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45097</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45019</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45457</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45463</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45698</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45393</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45076</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>44089</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45152</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>44335</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45517</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45478</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45785</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45106</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>44830</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45785</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45105</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44621</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45174</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45461</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45786</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45328</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45328</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45481</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>44130</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45328</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45153</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>44805</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45479</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>44964</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45461</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45125</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45108</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>45438</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>44596</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>44789</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44474</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>44789</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>44582</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44551</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44551</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45674</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>44139</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45798.5558912037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>45211</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45240</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45517</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45560</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45230</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45231</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45799</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>44140</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45077</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>44068</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45120</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>45165</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>45810</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>45344</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>44844</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>45415</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>44461</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>44460</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>45214</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45050</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45322</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45281</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44495</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44833</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45225</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45281</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45694.86898148148</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45692</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>45674</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44817</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45141</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45141</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45461</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>44699</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45099</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45215</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45215</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45196</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45761</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44406</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44886</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44523</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45483</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44860</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45470</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44838</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44483</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44678</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45239</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45169</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44151</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>45478</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45475</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45852</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45852</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45852</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45852</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44840</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>44858</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45845</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44970</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45672</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>45194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45238</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45475</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>44099</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44664</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45813</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45813</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44602</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45393</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45483</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>44112</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>44089</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45518</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45362</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45460</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45531</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45362</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>44712</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44491</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45096</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45393</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45393</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44994</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44173</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44985</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>44130</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44130</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44638</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45169</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>45204</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45153</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45822</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44212</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45348</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45348</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>45845</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44963</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45758</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44760</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44146</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45827</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>45827</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44587</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44889</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>45870</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45827</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45827</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45163</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>44853</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45477</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>45726.64574074074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>44518</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44851</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44957</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45636</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45302</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45322</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>44895</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45833</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45268</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45547</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>44965</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45833</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>44519</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45352</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45853</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45006</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44886</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44888</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>45184</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44195</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45700</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44099</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45328</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>45229</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44158</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>44980</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>44995</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>44831</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>44238</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45547</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44082</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>44172</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45328.47</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45167</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45026</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44623</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>44159</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45478</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>45384</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>44964</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45842</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45842</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>44602</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>44776</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>44103</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>44232</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45590</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>44449</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44445</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45772.63715277778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>44602</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45247</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>44266</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45016</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>44411</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>44212</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>44250</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>44600</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45463</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>45107</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>44173</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>44160</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45223</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45762</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>44130</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45316</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>44797</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45565</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44142</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>44942</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45604</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45204</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>44643</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44461</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44922</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45230</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44790</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45386</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44905</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>44694</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45061</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45001</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45001</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>44140</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>44968</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45594</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>45594</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>44964</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>45001</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>44987</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>44995</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>44602</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45006</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>45096</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>45666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>44964</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44816</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45245</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44708</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45222</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45075</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45547</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>45041</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>44169</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45204</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>44795</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
         <v>44694</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>45268</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>45168</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45563</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45071</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44781</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44781</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45147</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45189</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>44978</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44858</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>44467</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45509</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>45386</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>44060</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>44817</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>44085</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>44061</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>44977</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44442</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>44603</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45226</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45688</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45098</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>44075</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45477</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45182</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>44784</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>44603</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>44840</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>44231</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45019</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>44871</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>45160</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44844</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44823</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44859</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44977</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44386</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45516</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>44862</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>44074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44908</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>45016</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>45110</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>45677</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>45214</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42979,7 +42979,7 @@
         <v>45033</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44895</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45209</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44466</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44909</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>45050</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44862</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44985</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44974</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44945</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45154</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>44963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45205</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45211</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45057</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>44433</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>45231</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>44852</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>44886</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45667</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44510,7 +44510,7 @@
         <v>45076</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>44480</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>44440</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>44110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45457</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>44977</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>44855</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>44865</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45366</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>44934</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>44809</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>44825</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>44155</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>44467</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45281</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>44140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45075</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>44147</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>44848</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45214</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>44887</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>44483</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45231</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45229</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45098</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>44957</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>44957</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>45697</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45692</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>45001</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45001</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45601</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>45345</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45013</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45733</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>44995</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>44434</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>45057</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>44223</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>44876</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44238</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45062</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44473</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>44972</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45649</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>44169</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>45799</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>44068</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45099</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45666</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45013</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>45014</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44536</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44809</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44512</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44602</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>44546</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44733</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44839</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45231</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>44889</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45814</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45229</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44671</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45077</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>44995</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44099</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>44483</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45183</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44599</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>45184</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44831</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44995</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45133</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44749</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44803</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44393</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44419</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44299</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44299</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44824</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>44430</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>44853</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44546</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44553</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44519</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44323</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44090</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44166</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44265</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44423</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44407</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44512</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44266</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44266</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44468</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44476</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44599</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44628</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44824</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>44467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44602</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44719</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44391</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44417</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44466</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44496</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44480</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44719</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44370</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44102</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44725</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44468</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44251</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44619</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44168</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44426</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44581</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44256</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44169</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44266</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44265</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44299</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44712</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44783</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44783</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44449</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44783</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44351</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44130</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44510</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44264</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44099</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44495</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44701</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44683</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44550</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>44475</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44412</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44426</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44182</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44182</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44085</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44415</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44571</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44455</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>44601</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>44455</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>44607</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44260</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44797</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44725</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44616</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44832</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44725</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44411</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44522</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44526</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44369</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44840</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44531</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44062</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44238</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44523</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44375</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44789</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44827</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44467</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44141</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44725</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44169</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44270</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44266</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44512</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44762</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44463</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44790</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44605</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44225</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>44473</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44539</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44439</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44824</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44393</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44641</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44480</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44847</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45070</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44602</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>44706</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44837</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44838</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44859</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44696</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>44797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44242</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>45414</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44166</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45107</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45595</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45697</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45697</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44434</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45177</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45694</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45188</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>44488</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45362</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>44837</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45677</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44888</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44789</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45142</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44319</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44551</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45230</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44875</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44888</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44888</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45393</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44992</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45208</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44945</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45100</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44952</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45678</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45547</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45329</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>44362</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>44412</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45666</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44859</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45215</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>45322</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>44628</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45180</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45002</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>44601</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45097</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45019</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45457</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45463</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45698</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45393</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45076</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>44089</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45152</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>44335</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45517</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45478</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45785</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45106</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>44830</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45785</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45105</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44621</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45174</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45461</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45786</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45328</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45328</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45481</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>44130</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45328</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45153</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>44805</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45479</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>44964</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45461</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45125</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45108</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>45438</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>44596</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>44789</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44474</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>44789</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>44582</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44551</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44551</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45674</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>44139</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45798.5558912037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>45211</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45240</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45517</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45560</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45230</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45231</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45799</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>44140</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45077</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>44068</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45120</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>45165</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>45810</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>45344</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>44844</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>45415</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>44461</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>44460</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>45214</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45050</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45322</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45281</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44495</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44833</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45225</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45281</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45694.86898148148</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45692</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>45674</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44817</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45141</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45141</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45461</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>44699</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45099</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45215</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45215</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45196</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45761</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44406</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>44886</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44523</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45483</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44860</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45470</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44838</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44483</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44678</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45239</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45169</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44151</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>45478</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45475</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45852</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45852</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45852</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45852</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44840</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>44858</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45845</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44970</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45672</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>45194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45238</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45475</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>44099</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44664</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45813</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45813</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44602</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45393</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45483</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>44112</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>44089</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45518</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45362</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45460</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45531</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45362</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>44712</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44491</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45096</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45393</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45393</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44994</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44173</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44985</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>44130</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44130</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>44638</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45169</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>45204</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45153</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45822</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44212</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45348</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45348</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>45845</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44963</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45758</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44760</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>44146</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45827</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>45827</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44587</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44889</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>45870</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45827</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45827</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45163</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>44853</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45477</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>45726.64574074074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>44518</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44851</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44957</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45636</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45302</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45322</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>44895</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45833</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45268</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45547</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>44965</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45833</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>44519</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45352</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45853</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45006</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44886</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44888</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>45184</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44195</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45700</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44099</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45328</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>45229</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44158</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>44980</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>44995</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>44831</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>44238</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45547</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44082</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>44172</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45328.47</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45167</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45026</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44623</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>44159</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45478</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>45384</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>44964</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45842</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45842</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>44602</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>44776</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>44103</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>44232</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45590</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>44449</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44445</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45772.63715277778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>44602</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45247</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>44266</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45016</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>44411</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>44212</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>44250</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>44600</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45463</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>45107</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>44173</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>44160</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45223</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45762</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>44130</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45316</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>44797</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45565</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44142</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>44942</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45604</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45204</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>44643</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>44461</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44922</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45230</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44790</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45386</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44905</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>44694</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45061</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45001</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45001</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>44140</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>44968</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45594</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>45594</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>44964</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>45001</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>44987</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>44995</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>44602</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45006</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>45096</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>45666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>44964</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>44816</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45245</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>44708</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45222</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45075</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45547</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>45041</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>44169</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45204</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>44795</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
         <v>44694</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>45268</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>45168</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45563</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45071</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44781</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44781</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45147</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45189</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>44978</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>44858</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>44467</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45509</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>45386</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>44060</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>44817</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>44085</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>44061</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>44977</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44442</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>44603</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45226</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45688</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45098</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>44075</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45477</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45182</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>44784</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>44603</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>44840</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>44231</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45019</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>44871</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>45160</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44844</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44823</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44859</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44977</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44386</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45516</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>44862</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>44074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44908</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>45016</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>45110</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>45191</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>45677</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>45214</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42979,7 +42979,7 @@
         <v>45033</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44895</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45209</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44466</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44909</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>45050</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44862</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44985</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44974</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44945</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45154</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>44963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45205</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45211</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45057</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>44433</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>45231</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>44852</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>44886</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45667</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44510,7 +44510,7 @@
         <v>45076</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>44480</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>44440</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>44110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45457</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>44977</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>44855</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>44865</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45366</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>44934</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>44809</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>44825</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>44155</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>44467</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45281</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>44140</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45075</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>44147</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>44848</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45214</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>44887</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>44483</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45231</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45189</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45229</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45098</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>44957</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>44957</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>44965</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>45697</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45692</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>45001</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45001</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45601</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>45345</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45013</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45733</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>44995</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>44434</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>45057</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>44223</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44876</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>45852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45062</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44238</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44169</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>45649</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44972</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>44068</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45666</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45013</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44809</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45099</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45014</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>45799</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44481</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>44536</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44512</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44602</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44546</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44733</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>44839</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44671</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45184</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45077</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>44099</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44749</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>44831</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45183</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44599</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>45229</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44995</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44803</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45814</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45231</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44995</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44889</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45133</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44393</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44419</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44299</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>44299</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44824</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44430</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44853</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44546</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44553</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>44519</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44323</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44090</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44265</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44166</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44223</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44423</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44407</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44512</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44266</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44266</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44468</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44476</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44599</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44628</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44824</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44602</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44536</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44719</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44391</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44417</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44466</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44496</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44480</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44719</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44370</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44102</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>44725</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>44468</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>44619</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44515</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>44168</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44426</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44251</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44581</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>44256</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44169</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44266</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44265</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>44299</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44712</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44783</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44783</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44449</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44351</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44783</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44510</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44130</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44264</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>44099</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44495</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>44496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44701</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>44683</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>44475</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44550</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44412</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44426</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44182</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>44182</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44085</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44415</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44571</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44455</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44601</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44455</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>44455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44641</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44602</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44607</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>44706</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44837</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44838</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>44480</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>44260</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>44797</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44616</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44832</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44725</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44522</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>44369</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>44725</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>44411</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>44840</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44526</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>44238</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44531</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44523</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>44581</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>44375</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44789</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44141</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44467</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>44169</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44827</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44270</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44266</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44512</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>44762</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44539</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>44225</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>44439</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>44605</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44824</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>44473</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45667</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>44173</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44463</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44865</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>44099</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>45438</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45016</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>45328</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44977</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>44977</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45111</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45165</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44445</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44158</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>45188</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>44393</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>44768</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45204</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45457</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>44142</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44823</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>44643</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45108</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44790</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45362</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44957</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44934</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45517</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44851</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45184</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>44212</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45594</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45594</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>44858</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44978</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44886</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45384</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44195</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45204</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44474</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45483</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>44173</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45461</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44965</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>44964</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>45697</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45697</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>45160</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>44694</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45110</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>45393</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44840</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44895</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44172</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45205</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45006</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>44942</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45415</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>44483</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45141</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45239</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44411</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44995</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>44964</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44460</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>44461</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45071</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>44963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>44992</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45758</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45516</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45169</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>45153</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>45329</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>44488</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45167</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>44963</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>44699</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45019</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>44467</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45057</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44582</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44840</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44844</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44250</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44362</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>44957</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45386</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>44146</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45386</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45120</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44440</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45462</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>45328.47</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44231</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45478</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45016</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45050</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45636</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44980</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44140</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45674</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>44789</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>44789</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45604</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>44155</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>44212</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>45761</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>44461</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45547</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45762</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45182</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>44789</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45393</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45001</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45345</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>44551</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44551</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45547</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44825</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45281</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45477</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>44977</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45666</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44110</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44412</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44847</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45726.64574074074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45222</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45698</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>44945</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45672</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44169</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44970</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44909</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>44266</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44859</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>45565</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45785</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>44433</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44781</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>44075</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>45414</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45785</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>44837</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45196</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>44621</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45189</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45001</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>44406</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45019</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44859</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45461</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45517</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44888</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44809</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45141</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45152</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45013</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45786</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44335</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44130</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44483</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>45096</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45231</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>44987</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>45154</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>44159</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>44887</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>44831</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45457</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>44678</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>44518</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>44862</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45002</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45208</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45393</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>45362</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45461</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45153</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>44139</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45147</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45163</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45674</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>44871</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45475</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>44696</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45247</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44964</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>44994</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>44795</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45798.5558912037</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45231</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45560</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>45322</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45463</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45758</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45245</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45099</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>44895</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>44830</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>45240</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>45148</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45096</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>45077</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45344</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45810</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44968</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45226</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44603</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>44603</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>45215</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45001</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>44089</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45479</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45097</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45601</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44797</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45481</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45268</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45733</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45230</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>44434</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>44965</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>44140</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45100</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45547</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>44922</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>44852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>44957</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44797</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45076</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45692</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45852</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45813</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45813</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45328</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44112</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>44089</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45852</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>44495</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>45209</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45322</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45852</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45852</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45852</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45214</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44587</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45677</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44945</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44664</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45281</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45281</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45125</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44130</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45105</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45191</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45107</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45231</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>45531</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>45483</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44638</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45348</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>44074</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>44760</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>44099</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>44888</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>44085</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>45509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44838</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45822</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45214</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>45845</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44694</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>44082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>45547</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44602</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44466</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>44601</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>44952</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45827</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>45827</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>45352</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45393</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45393</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45076</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45075</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45075</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45194</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>45827</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45463</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45518</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45827</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45169</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>44862</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45098</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>44848</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45362</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45168</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45677</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>45870</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>44523</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>44860</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>44602</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         <v>45211</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45106</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>44889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45833</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>45833</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44602</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44995</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44844</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45026</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>44817</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>44708</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45678</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45180</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>45470</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45142</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>45666</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44386</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>45215</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>45215</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>44776</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45107</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44875</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>44480</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45268</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>45204</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>45316</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>45853</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45098</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>45302</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45590</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>44853</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44068</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45041</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>44886</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>45211</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>45460</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45322</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>44232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>45033</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45230</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>44238</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>44712</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45842</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>44551</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>45230</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>44491</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45223</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45478</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>45475</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>44151</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>45595</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>45700</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>44833</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45225</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45842</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>44855</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45177</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>45366</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>45852</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44805</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44166</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43351,7 +43351,7 @@
         <v>45694</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44659</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44103</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45885</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44985</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45697</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>44888</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>44888</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>44623</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>44602</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>44602</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>44449</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>44816</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>45478</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44519</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>45890</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>45890</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44573,7 +44573,7 @@
         <v>45890</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>45174</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>44467</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>45845</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>45891</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>45891.58381944444</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45688</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>44130</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45477</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>44974</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>44439</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>44160</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>44886</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>44596</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45238</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45006</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44442</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44319</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45692</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45214</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45348</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45189</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>44140</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45061</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45001</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45001</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>44130</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45328</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45328</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>44600</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>44858</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>44957</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>44781</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>44905</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45229</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>44628</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47188,7 +47188,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>44147</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>44242</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>44995</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>44434</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>45057</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>44223</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44876</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>45852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45062</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44238</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44169</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>45649</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44972</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>44068</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45666</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45013</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44809</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45099</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45014</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>45799</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44481</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>44536</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44512</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44602</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44546</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44733</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>44839</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44671</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45184</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45077</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>44099</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44749</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>44831</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45183</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44599</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>45229</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44995</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44803</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45814</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45231</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44995</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44889</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45133</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44393</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44419</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44299</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>44299</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44824</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44430</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44853</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44546</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44553</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>44519</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44323</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44090</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44265</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44166</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44223</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44423</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44407</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44512</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44266</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44266</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44468</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44476</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44599</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44628</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44824</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44602</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44536</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44719</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44391</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44417</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44466</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44496</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44480</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44719</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44370</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44102</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>44725</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>44468</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>44619</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44515</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>44168</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44426</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44251</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44581</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>44256</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44169</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44266</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44265</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>44299</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44712</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44783</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44783</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44449</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44351</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44783</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44510</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44130</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44264</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>44099</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44495</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>44496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44701</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>44683</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>44475</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44550</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44412</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44426</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44182</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>44182</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44085</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44415</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44571</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44455</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44601</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44455</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>44455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44641</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44602</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44607</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>44706</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44837</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44838</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>44480</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>44260</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>44797</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44616</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44832</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44725</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44522</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>44369</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>44725</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>44411</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>44840</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44526</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>44238</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44531</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44523</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>44581</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>44375</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44789</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44141</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44467</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>44169</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44827</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44270</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44266</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44512</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>44762</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44539</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>44225</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>44439</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>44605</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44824</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>44473</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>45667</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>44173</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44463</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44865</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>44099</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>45438</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45016</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>45328</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44977</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>44977</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45111</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45165</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44445</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44158</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>45188</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>44393</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>44768</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45204</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45457</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>44142</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44823</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>44643</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45108</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44790</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45362</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44957</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44934</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45517</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44851</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45184</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>44212</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45594</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45594</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>44858</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44978</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44886</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45384</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44195</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45204</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44474</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45483</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>44173</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45461</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44965</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>44964</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>45697</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45697</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>45160</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>44694</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45110</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>45393</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44840</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44895</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44172</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45205</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45006</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>44942</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45415</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>44483</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45141</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45239</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44411</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44995</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>44964</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44460</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>44461</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45071</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>44963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>44992</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45758</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45516</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45169</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>45153</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>45329</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>44488</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45167</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>44963</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>44699</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45019</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>44467</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45057</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44582</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44840</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44844</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44250</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44362</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>44957</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45386</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>44146</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45386</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45120</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44440</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45462</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>45328.47</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44231</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45478</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45016</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45050</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45636</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44980</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44140</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45674</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>44789</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>44789</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45604</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>44155</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>44212</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>45761</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>44461</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45547</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45762</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45182</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>44789</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45393</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45001</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45345</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>44551</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44551</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45547</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44825</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45281</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45477</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>44977</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45666</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>44110</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44412</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44847</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45726.64574074074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45222</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45698</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>44945</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45672</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44169</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44970</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44909</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>44266</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44859</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>45565</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45785</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>44433</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44781</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>44075</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>45414</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45785</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>44837</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45196</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>44621</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45189</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45001</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>44406</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45019</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44859</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45461</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45517</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>44888</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>44809</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45141</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45152</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45013</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45786</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44335</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44130</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44483</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>45096</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45231</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>44987</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>45154</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>44159</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>44887</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>44831</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45457</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>44678</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>44518</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>44862</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45002</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45208</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45393</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>45362</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45461</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45153</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>44139</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45147</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45163</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45674</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>44871</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45475</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>44696</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45247</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44964</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>44994</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>44795</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45798.5558912037</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45231</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45560</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>45322</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45463</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45758</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45245</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45099</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>44895</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>44830</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>45240</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>45148</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45096</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>45077</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45344</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45810</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44968</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45226</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44603</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>44603</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>45215</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45001</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>44089</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45479</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45097</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45601</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44797</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45481</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45268</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45733</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45230</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>44434</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>44965</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>44140</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45100</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45547</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>44922</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>44852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>44957</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44797</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45076</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45692</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45852</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45813</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45813</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45328</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44112</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>44089</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45852</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>44495</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>45209</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45322</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45852</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45852</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45852</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45214</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44587</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45677</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44945</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44664</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45281</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45281</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45125</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44130</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45105</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45191</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45107</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45231</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>45531</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>45483</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44638</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45348</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>44074</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>44760</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>44099</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>44888</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>44085</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>45509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44838</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45822</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45214</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>45845</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44694</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>44082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>45547</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44602</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44466</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>44601</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>44952</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45827</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>45827</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>45352</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45393</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45393</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45076</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45075</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45075</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45194</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>45827</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45463</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45518</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45827</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45169</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>44862</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45098</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>44848</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45362</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45168</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45677</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>45870</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>44523</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>44860</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>44602</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         <v>45211</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45106</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>44889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45833</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>45833</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44602</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44995</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44844</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45026</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>44817</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>44708</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45678</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45180</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>45470</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45142</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>45666</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44386</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>45215</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>45215</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>44776</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45107</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44875</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>44480</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45268</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>45204</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>45316</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>45853</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45098</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>45302</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45590</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>44853</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44068</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45041</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>44886</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>45211</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>45460</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45322</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>44232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>45033</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45230</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>44238</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>44712</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45842</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>44551</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>45230</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>44491</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45223</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45478</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>45475</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>44151</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>45595</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>45700</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>44833</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45225</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45842</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>44855</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45177</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>45366</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>45852</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44805</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44166</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43351,7 +43351,7 @@
         <v>45694</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44659</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44103</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45885</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44985</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45697</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>44888</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>44888</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>44623</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>44602</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>44602</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>44449</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>44816</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>45478</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44519</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>45890</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>45890</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44573,7 +44573,7 @@
         <v>45890</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>45174</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>44467</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>45845</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>45891</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>45891.58381944444</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45688</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>44130</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45477</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>44974</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>44439</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>44160</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45229</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>44886</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>44596</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45238</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45006</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44442</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44319</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45692</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45214</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45348</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45189</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>44140</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45061</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45001</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45001</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>44130</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45328</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45328</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>44600</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>44858</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>44957</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>44781</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>44905</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45229</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>44628</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47188,7 +47188,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>44147</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>44242</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         <v>13</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -604,19 +604,20 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Blackticka
 Knärot
 Rotfingersvamp
+Blå taggsvamp
 Dofttaggsvamp
 Fyrflikig jordstjärna
 Granticka
@@ -644,7 +645,10 @@
 Grönpyrola
 Mindre märgborre
 Rödgul trumpetsvamp
+Skarp dropptaggsvamp
+Vedticka
 Vågbandad barkbock
+Vårärt
 Kungsfågel
 Tjäder
 Huggorm
@@ -699,7 +703,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,7 +808,7 @@
         <v>44434</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,7 +907,7 @@
         <v>44995</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,7 +1015,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1113,7 @@
         <v>44876</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,7 +1205,7 @@
         <v>45057</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,7 +1301,7 @@
         <v>45852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1388,7 +1392,7 @@
         <v>44223</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,7 +1492,7 @@
         <v>44238</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,7 +1582,7 @@
         <v>44473</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1668,7 +1672,7 @@
         <v>45062</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,7 +1762,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,7 +1860,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1948,7 @@
         <v>44972</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2040,7 +2044,7 @@
         <v>45649</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2127,7 +2131,7 @@
         <v>44169</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2223,7 +2227,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2313,7 +2317,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2403,7 +2407,7 @@
         <v>44481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2498,7 +2502,7 @@
         <v>45099</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2584,7 +2588,7 @@
         <v>45013</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2674,7 +2678,7 @@
         <v>45799</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2764,7 @@
         <v>45666</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2846,7 +2850,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2932,7 +2936,7 @@
         <v>45014</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3022,7 +3026,7 @@
         <v>44536</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3108,7 +3112,7 @@
         <v>44809</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3194,7 +3198,7 @@
         <v>44512</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3283,7 +3287,7 @@
         <v>44602</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3368,7 +3372,7 @@
         <v>44546</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3453,7 +3457,7 @@
         <v>44733</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3538,7 +3542,7 @@
         <v>44839</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3623,7 +3627,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3713,7 +3717,7 @@
         <v>44889</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3802,7 @@
         <v>45814</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3892,7 @@
         <v>45231</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3977,7 @@
         <v>44671</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4062,7 +4066,7 @@
         <v>45077</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4152,7 +4156,7 @@
         <v>45229</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4241,7 +4245,7 @@
         <v>44483</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4326,7 +4330,7 @@
         <v>45183</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4411,7 +4415,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4501,7 +4505,7 @@
         <v>45184</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4586,7 +4590,7 @@
         <v>44995</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4676,7 +4680,7 @@
         <v>44099</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4766,7 +4770,7 @@
         <v>45133</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4851,7 +4855,7 @@
         <v>44803</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4936,7 +4940,7 @@
         <v>44599</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5021,7 +5025,7 @@
         <v>44831</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5106,7 +5110,7 @@
         <v>44995</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5196,7 +5200,7 @@
         <v>44749</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5281,7 +5285,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5374,7 @@
         <v>44393</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5431,7 @@
         <v>44419</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5488,7 @@
         <v>44299</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5545,7 @@
         <v>44299</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5602,7 @@
         <v>44824</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5655,7 +5659,7 @@
         <v>44853</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5717,7 +5721,7 @@
         <v>44430</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5774,7 +5778,7 @@
         <v>44473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5851,7 +5855,7 @@
         <v>44546</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5908,7 +5912,7 @@
         <v>44553</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5965,7 +5969,7 @@
         <v>44519</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6027,7 +6031,7 @@
         <v>44323</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6084,7 +6088,7 @@
         <v>44090</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6141,7 +6145,7 @@
         <v>44166</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6203,7 +6207,7 @@
         <v>44265</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6260,7 +6264,7 @@
         <v>44223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6317,7 +6321,7 @@
         <v>44423</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6374,7 +6378,7 @@
         <v>44407</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6431,7 +6435,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6488,7 +6492,7 @@
         <v>44512</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6545,7 +6549,7 @@
         <v>44266</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6602,7 +6606,7 @@
         <v>44266</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6659,7 +6663,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6721,7 +6725,7 @@
         <v>44468</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6778,7 +6782,7 @@
         <v>44476</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6835,7 +6839,7 @@
         <v>44536</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6892,7 +6896,7 @@
         <v>44599</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6953,7 @@
         <v>44628</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7010,7 @@
         <v>44824</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7063,7 +7067,7 @@
         <v>44467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7120,7 +7124,7 @@
         <v>44602</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7177,7 +7181,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7234,7 +7238,7 @@
         <v>44536</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7291,7 +7295,7 @@
         <v>44719</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7348,7 +7352,7 @@
         <v>44391</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7405,7 +7409,7 @@
         <v>44417</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7462,7 +7466,7 @@
         <v>44466</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7519,7 +7523,7 @@
         <v>44496</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7576,7 +7580,7 @@
         <v>44480</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7638,7 +7642,7 @@
         <v>44719</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7695,7 +7699,7 @@
         <v>44370</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7752,7 +7756,7 @@
         <v>44585</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7809,7 +7813,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7866,7 +7870,7 @@
         <v>44102</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7923,7 +7927,7 @@
         <v>44725</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7980,7 +7984,7 @@
         <v>44619</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8037,7 +8041,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8094,7 +8098,7 @@
         <v>44251</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8151,7 +8155,7 @@
         <v>44468</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8208,7 +8212,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8265,7 +8269,7 @@
         <v>44168</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8322,7 +8326,7 @@
         <v>44515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8379,7 +8383,7 @@
         <v>44426</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8436,7 +8440,7 @@
         <v>44581</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8493,7 +8497,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8555,7 +8559,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8612,7 +8616,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8669,7 +8673,7 @@
         <v>44256</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8726,7 +8730,7 @@
         <v>44169</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8783,7 +8787,7 @@
         <v>44266</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8840,7 +8844,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8897,7 +8901,7 @@
         <v>44265</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8954,7 +8958,7 @@
         <v>44299</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9011,7 +9015,7 @@
         <v>44712</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9068,7 +9072,7 @@
         <v>44783</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9125,7 +9129,7 @@
         <v>44783</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9182,7 +9186,7 @@
         <v>44449</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9239,7 +9243,7 @@
         <v>44783</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9296,7 +9300,7 @@
         <v>44130</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9353,7 +9357,7 @@
         <v>44130</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9410,7 +9414,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9467,7 +9471,7 @@
         <v>44510</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9529,7 +9533,7 @@
         <v>44351</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9586,7 +9590,7 @@
         <v>44264</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9648,7 +9652,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9705,7 +9709,7 @@
         <v>44099</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9762,7 +9766,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9819,7 +9823,7 @@
         <v>44495</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9876,7 +9880,7 @@
         <v>44496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9933,7 +9937,7 @@
         <v>44701</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9990,7 +9994,7 @@
         <v>44683</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10047,7 +10051,7 @@
         <v>44550</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10109,7 +10113,7 @@
         <v>44475</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10166,7 +10170,7 @@
         <v>44412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10223,7 +10227,7 @@
         <v>44182</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10280,7 +10284,7 @@
         <v>44182</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10337,7 +10341,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10394,7 +10398,7 @@
         <v>44426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10451,7 +10455,7 @@
         <v>44415</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10508,7 +10512,7 @@
         <v>44571</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10565,7 +10569,7 @@
         <v>44085</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10622,7 +10626,7 @@
         <v>44455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10679,7 +10683,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10736,7 +10740,7 @@
         <v>44455</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10793,7 +10797,7 @@
         <v>44455</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10850,7 +10854,7 @@
         <v>44601</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10907,7 +10911,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10964,7 +10968,7 @@
         <v>44602</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11021,7 +11025,7 @@
         <v>44706</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11078,7 +11082,7 @@
         <v>44837</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11135,7 +11139,7 @@
         <v>44838</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11192,7 +11196,7 @@
         <v>44607</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11249,7 +11253,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11306,7 +11310,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11363,7 +11367,7 @@
         <v>44480</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11425,7 +11429,7 @@
         <v>44260</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11487,7 +11491,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11544,7 +11548,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11601,7 +11605,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11658,7 +11662,7 @@
         <v>44797</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11715,7 +11719,7 @@
         <v>44725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11772,7 +11776,7 @@
         <v>44725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11829,7 +11833,7 @@
         <v>44411</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11886,7 +11890,7 @@
         <v>44526</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11943,7 +11947,7 @@
         <v>44616</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12005,7 +12009,7 @@
         <v>44369</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12062,7 +12066,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12119,7 +12123,7 @@
         <v>44832</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12176,7 +12180,7 @@
         <v>44522</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12238,7 +12242,7 @@
         <v>44531</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12295,7 +12299,7 @@
         <v>44840</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12352,7 +12356,7 @@
         <v>44581</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12409,7 +12413,7 @@
         <v>44238</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12466,7 +12470,7 @@
         <v>44789</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12523,7 +12527,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12580,7 +12584,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12637,7 +12641,7 @@
         <v>44467</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12694,7 +12698,7 @@
         <v>44523</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12751,7 +12755,7 @@
         <v>44827</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12808,7 +12812,7 @@
         <v>44375</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12885,7 +12889,7 @@
         <v>44169</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12947,7 +12951,7 @@
         <v>44141</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13004,7 +13008,7 @@
         <v>44725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13061,7 +13065,7 @@
         <v>44270</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13123,7 +13127,7 @@
         <v>44266</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13180,7 +13184,7 @@
         <v>44463</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13237,7 +13241,7 @@
         <v>44512</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13294,7 +13298,7 @@
         <v>44762</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13356,7 +13360,7 @@
         <v>44225</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13413,7 +13417,7 @@
         <v>44605</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13470,7 +13474,7 @@
         <v>44790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13532,7 +13536,7 @@
         <v>44473</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13594,7 +13598,7 @@
         <v>44539</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13656,7 +13660,7 @@
         <v>44439</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13713,7 +13717,7 @@
         <v>44393</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13770,7 +13774,7 @@
         <v>44768</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13827,7 +13831,7 @@
         <v>44824</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13884,7 +13888,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13941,7 +13945,7 @@
         <v>44641</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13998,7 +14002,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14055,7 +14059,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14112,7 +14116,7 @@
         <v>45678</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14174,7 +14178,7 @@
         <v>45070</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14236,7 +14240,7 @@
         <v>44859</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14293,7 +14297,7 @@
         <v>44859</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14350,7 +14354,7 @@
         <v>45215</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14407,7 +14411,7 @@
         <v>44847</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14464,7 +14468,7 @@
         <v>44696</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14521,7 +14525,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14578,7 +14582,7 @@
         <v>44797</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14635,7 +14639,7 @@
         <v>44242</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14697,7 +14701,7 @@
         <v>44166</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14759,7 +14763,7 @@
         <v>45107</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14821,7 +14825,7 @@
         <v>45697</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14878,7 +14882,7 @@
         <v>45697</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14935,7 +14939,7 @@
         <v>45677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14992,7 +14996,7 @@
         <v>44434</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15049,7 +15053,7 @@
         <v>45177</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15106,7 +15110,7 @@
         <v>44488</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15163,7 +15167,7 @@
         <v>45595</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15220,7 +15224,7 @@
         <v>44789</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15277,7 +15281,7 @@
         <v>45694</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15334,7 +15338,7 @@
         <v>45188</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15396,7 +15400,7 @@
         <v>44319</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15453,7 +15457,7 @@
         <v>45414</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15515,7 +15519,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15572,7 +15576,7 @@
         <v>45142</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15629,7 +15633,7 @@
         <v>45362</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15686,7 +15690,7 @@
         <v>44837</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15743,7 +15747,7 @@
         <v>44551</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15800,7 +15804,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15857,7 +15861,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15914,7 +15918,7 @@
         <v>44888</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15971,7 +15975,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16028,7 +16032,7 @@
         <v>44945</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16085,7 +16089,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16147,7 +16151,7 @@
         <v>44875</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16209,7 +16213,7 @@
         <v>45230</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16271,7 +16275,7 @@
         <v>45547</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16328,7 +16332,7 @@
         <v>45393</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16390,7 +16394,7 @@
         <v>44992</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16452,7 +16456,7 @@
         <v>44888</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16509,7 +16513,7 @@
         <v>44888</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16566,7 +16570,7 @@
         <v>44412</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16623,7 +16627,7 @@
         <v>45666</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16685,7 +16689,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16742,7 +16746,7 @@
         <v>45329</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16799,7 +16803,7 @@
         <v>45208</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16856,7 +16860,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16913,7 +16917,7 @@
         <v>45100</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16970,7 +16974,7 @@
         <v>44952</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17027,7 +17031,7 @@
         <v>44362</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17089,7 +17093,7 @@
         <v>45322</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17146,7 +17150,7 @@
         <v>44628</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17203,7 +17207,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17260,7 +17264,7 @@
         <v>45698</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17317,7 +17321,7 @@
         <v>45180</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17374,7 +17378,7 @@
         <v>45457</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17431,7 +17435,7 @@
         <v>45106</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17488,7 +17492,7 @@
         <v>44830</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17545,7 +17549,7 @@
         <v>45002</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17607,7 +17611,7 @@
         <v>44601</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17664,7 +17668,7 @@
         <v>45097</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17721,7 +17725,7 @@
         <v>45019</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17783,7 +17787,7 @@
         <v>44805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17840,7 +17844,7 @@
         <v>44335</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17897,7 +17901,7 @@
         <v>45463</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17954,7 +17958,7 @@
         <v>45517</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18011,7 +18015,7 @@
         <v>44789</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18068,7 +18072,7 @@
         <v>44474</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18125,7 +18129,7 @@
         <v>44789</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18182,7 +18186,7 @@
         <v>45120</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18239,7 +18243,7 @@
         <v>44844</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18296,7 +18300,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18358,7 +18362,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18415,7 +18419,7 @@
         <v>45415</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18472,7 +18476,7 @@
         <v>45393</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18534,7 +18538,7 @@
         <v>45076</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18591,7 +18595,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18648,7 +18652,7 @@
         <v>44461</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18705,7 +18709,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18762,7 +18766,7 @@
         <v>45785</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18819,7 +18823,7 @@
         <v>44460</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18876,7 +18880,7 @@
         <v>45322</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18933,7 +18937,7 @@
         <v>45281</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18990,7 +18994,7 @@
         <v>45152</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19047,7 +19051,7 @@
         <v>44495</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19104,7 +19108,7 @@
         <v>45148</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19161,7 +19165,7 @@
         <v>44833</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19218,7 +19222,7 @@
         <v>45785</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19275,7 +19279,7 @@
         <v>45281</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19332,7 +19336,7 @@
         <v>45478</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19389,7 +19393,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19451,7 +19455,7 @@
         <v>45461</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19508,7 +19512,7 @@
         <v>45786</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19565,7 +19569,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19622,7 +19626,7 @@
         <v>44130</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19679,7 +19683,7 @@
         <v>45462</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19736,7 +19740,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19793,7 +19797,7 @@
         <v>45461</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19850,7 +19854,7 @@
         <v>45099</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19907,7 +19911,7 @@
         <v>45105</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19969,7 +19973,7 @@
         <v>44621</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20026,7 +20030,7 @@
         <v>45174</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20088,7 +20092,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20145,7 +20149,7 @@
         <v>44406</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20202,7 +20206,7 @@
         <v>44886</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20259,7 +20263,7 @@
         <v>45328</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20316,7 +20320,7 @@
         <v>45328</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20378,7 +20382,7 @@
         <v>45481</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20435,7 +20439,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20492,7 +20496,7 @@
         <v>45328</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20549,7 +20553,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20606,7 +20610,7 @@
         <v>44523</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20663,7 +20667,7 @@
         <v>45483</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20720,7 +20724,7 @@
         <v>44860</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20777,7 +20781,7 @@
         <v>45470</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20834,7 +20838,7 @@
         <v>45153</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20896,7 +20900,7 @@
         <v>44838</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20953,7 +20957,7 @@
         <v>45461</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21010,7 +21014,7 @@
         <v>44483</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21067,7 +21071,7 @@
         <v>45479</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21124,7 +21128,7 @@
         <v>45239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21181,7 +21185,7 @@
         <v>45169</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21243,7 +21247,7 @@
         <v>44151</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21300,7 +21304,7 @@
         <v>45478</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21362,7 +21366,7 @@
         <v>45475</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21419,7 +21423,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21481,7 +21485,7 @@
         <v>44964</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21538,7 +21542,7 @@
         <v>45125</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21595,7 +21599,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21652,7 +21656,7 @@
         <v>45108</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21709,7 +21713,7 @@
         <v>45674</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21766,7 +21770,7 @@
         <v>44840</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21823,7 +21827,7 @@
         <v>44858</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21880,7 +21884,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21937,7 +21941,7 @@
         <v>45438</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21994,7 +21998,7 @@
         <v>44596</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22051,7 +22055,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22108,7 +22112,7 @@
         <v>44970</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22165,7 +22169,7 @@
         <v>45672</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22222,7 +22226,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22279,7 +22283,7 @@
         <v>45798.5558912037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22341,7 +22345,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22398,7 +22402,7 @@
         <v>44582</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22455,7 +22459,7 @@
         <v>45475</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22512,7 +22516,7 @@
         <v>44099</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22569,7 +22573,7 @@
         <v>45240</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22631,7 +22635,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22688,7 +22692,7 @@
         <v>44551</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22745,7 +22749,7 @@
         <v>44551</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22802,7 +22806,7 @@
         <v>44602</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22859,7 +22863,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22916,7 +22920,7 @@
         <v>44139</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22973,7 +22977,7 @@
         <v>44602</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23030,7 +23034,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23087,7 +23091,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23144,7 +23148,7 @@
         <v>45560</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23201,7 +23205,7 @@
         <v>45393</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23258,7 +23262,7 @@
         <v>45483</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23315,7 +23319,7 @@
         <v>44112</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23377,7 +23381,7 @@
         <v>44089</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23434,7 +23438,7 @@
         <v>45518</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23491,7 +23495,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23548,7 +23552,7 @@
         <v>45231</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23605,7 +23609,7 @@
         <v>45799</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23662,7 +23666,7 @@
         <v>45362</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23719,7 +23723,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23776,7 +23780,7 @@
         <v>45211</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23833,7 +23837,7 @@
         <v>45460</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23890,7 +23894,7 @@
         <v>45362</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23947,7 +23951,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24004,7 +24008,7 @@
         <v>44491</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24061,7 +24065,7 @@
         <v>45517</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24118,7 +24122,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24180,7 +24184,7 @@
         <v>45393</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24237,7 +24241,7 @@
         <v>45393</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24294,7 +24298,7 @@
         <v>44994</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24351,7 +24355,7 @@
         <v>45810</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24408,7 +24412,7 @@
         <v>44173</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24470,7 +24474,7 @@
         <v>44985</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24527,7 +24531,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24584,7 +24588,7 @@
         <v>44130</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24641,7 +24645,7 @@
         <v>44130</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24698,7 +24702,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24755,7 +24759,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24812,7 +24816,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24869,7 +24873,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24926,7 +24930,7 @@
         <v>45230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24988,7 +24992,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25045,7 +25049,7 @@
         <v>45348</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25102,7 +25106,7 @@
         <v>45348</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25159,7 +25163,7 @@
         <v>44140</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25216,7 +25220,7 @@
         <v>45077</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25278,7 +25282,7 @@
         <v>44963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25335,7 +25339,7 @@
         <v>44151</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25392,7 +25396,7 @@
         <v>45165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25449,7 +25453,7 @@
         <v>45344</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25506,7 +25510,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25563,7 +25567,7 @@
         <v>44146</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25625,7 +25629,7 @@
         <v>45214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25682,7 +25686,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25739,7 +25743,7 @@
         <v>45050</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25801,7 +25805,7 @@
         <v>44889</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25878,7 +25882,7 @@
         <v>45813</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25935,7 +25939,7 @@
         <v>45813</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25992,7 +25996,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26049,7 +26053,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26106,7 +26110,7 @@
         <v>45225</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26163,7 +26167,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26220,7 +26224,7 @@
         <v>45531</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26277,7 +26281,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26334,7 +26338,7 @@
         <v>45692</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26396,7 +26400,7 @@
         <v>44957</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26458,7 +26462,7 @@
         <v>45636</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26515,7 +26519,7 @@
         <v>44638</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26572,7 +26576,7 @@
         <v>45674</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26629,7 +26633,7 @@
         <v>44817</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26686,7 +26690,7 @@
         <v>45141</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26743,7 +26747,7 @@
         <v>45141</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26800,7 +26804,7 @@
         <v>45547</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26857,7 +26861,7 @@
         <v>44699</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26914,7 +26918,7 @@
         <v>45215</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26971,7 +26975,7 @@
         <v>45215</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27028,7 +27032,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27090,7 +27094,7 @@
         <v>45822</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27147,7 +27151,7 @@
         <v>44195</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27204,7 +27208,7 @@
         <v>45196</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27266,7 +27270,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27323,7 +27327,7 @@
         <v>45845</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27380,7 +27384,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27442,7 +27446,7 @@
         <v>44158</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27504,7 +27508,7 @@
         <v>44980</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27566,7 +27570,7 @@
         <v>44659</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27623,7 +27627,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27680,7 +27684,7 @@
         <v>44995</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27742,7 +27746,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27804,7 +27808,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27866,7 +27870,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27923,7 +27927,7 @@
         <v>44678</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27980,7 +27984,7 @@
         <v>44238</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28037,7 +28041,7 @@
         <v>44172</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28094,7 +28098,7 @@
         <v>45827</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28151,7 +28155,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28208,7 +28212,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28265,7 +28269,7 @@
         <v>45827</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28322,7 +28326,7 @@
         <v>44623</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28379,7 +28383,7 @@
         <v>45870</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28436,7 +28440,7 @@
         <v>45827</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28493,7 +28497,7 @@
         <v>45827</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28550,7 +28554,7 @@
         <v>45384</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28612,7 +28616,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28669,7 +28673,7 @@
         <v>44964</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28726,7 +28730,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28783,7 +28787,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28840,7 +28844,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28902,7 +28906,7 @@
         <v>45194</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28959,7 +28963,7 @@
         <v>45590</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29016,7 +29020,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29073,7 +29077,7 @@
         <v>45238</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29130,7 +29134,7 @@
         <v>44445</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29187,7 +29191,7 @@
         <v>45833</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29244,7 +29248,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29301,7 +29305,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29358,7 +29362,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29415,7 +29419,7 @@
         <v>44664</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29472,7 +29476,7 @@
         <v>45247</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29529,7 +29533,7 @@
         <v>44266</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29586,7 +29590,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29643,7 +29647,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29700,7 +29704,7 @@
         <v>44600</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29757,7 +29761,7 @@
         <v>44712</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29814,7 +29818,7 @@
         <v>45096</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29871,7 +29875,7 @@
         <v>45223</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29928,7 +29932,7 @@
         <v>45833</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29985,7 +29989,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30047,7 +30051,7 @@
         <v>45169</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30104,7 +30108,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30161,7 +30165,7 @@
         <v>45204</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30218,7 +30222,7 @@
         <v>45153</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30275,7 +30279,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30332,7 +30336,7 @@
         <v>45762</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30389,7 +30393,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30446,7 +30450,7 @@
         <v>45316</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30503,7 +30507,7 @@
         <v>44797</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30560,7 +30564,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30617,7 +30621,7 @@
         <v>45565</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30674,7 +30678,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30731,7 +30735,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30793,7 +30797,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30850,7 +30854,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30907,7 +30911,7 @@
         <v>44212</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30964,7 +30968,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31021,7 +31025,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31083,7 +31087,7 @@
         <v>45604</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31140,7 +31144,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31197,7 +31201,7 @@
         <v>45204</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31259,7 +31263,7 @@
         <v>45758</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31316,7 +31320,7 @@
         <v>45758</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31373,7 +31377,7 @@
         <v>44760</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31430,7 +31434,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31487,7 +31491,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31544,7 +31548,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31601,7 +31605,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31658,7 +31662,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31715,7 +31719,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31772,7 +31776,7 @@
         <v>45163</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31829,7 +31833,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31886,7 +31890,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31948,7 +31952,7 @@
         <v>44643</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32005,7 +32009,7 @@
         <v>45477</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32062,7 +32066,7 @@
         <v>44461</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32119,7 +32123,7 @@
         <v>45230</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32176,7 +32180,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32238,7 +32242,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32295,7 +32299,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32352,7 +32356,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32409,7 +32413,7 @@
         <v>45061</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32466,7 +32470,7 @@
         <v>45001</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32523,7 +32527,7 @@
         <v>45001</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32580,7 +32584,7 @@
         <v>45842</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32637,7 +32641,7 @@
         <v>45842</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32694,7 +32698,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32751,7 +32755,7 @@
         <v>44968</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32808,7 +32812,7 @@
         <v>45594</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32865,7 +32869,7 @@
         <v>45001</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32922,7 +32926,7 @@
         <v>44987</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32979,7 +32983,7 @@
         <v>44518</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33041,7 +33045,7 @@
         <v>44851</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33103,7 +33107,7 @@
         <v>45700</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33160,7 +33164,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33217,7 +33221,7 @@
         <v>45302</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33274,7 +33278,7 @@
         <v>45322</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33331,7 +33335,7 @@
         <v>44895</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33388,7 +33392,7 @@
         <v>45096</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33445,7 +33449,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33502,7 +33506,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33559,7 +33563,7 @@
         <v>45666</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33616,7 +33620,7 @@
         <v>44964</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33673,7 +33677,7 @@
         <v>45885</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33730,7 +33734,7 @@
         <v>45268</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33787,7 +33791,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33844,7 +33848,7 @@
         <v>44439</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33901,7 +33905,7 @@
         <v>44965</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33958,7 +33962,7 @@
         <v>44519</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34020,7 +34024,7 @@
         <v>45352</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34077,7 +34081,7 @@
         <v>45041</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34134,7 +34138,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34191,7 +34195,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34253,7 +34257,7 @@
         <v>45006</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34315,7 +34319,7 @@
         <v>45852</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34372,7 +34376,7 @@
         <v>45853</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34429,7 +34433,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34486,7 +34490,7 @@
         <v>44886</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34543,7 +34547,7 @@
         <v>44888</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34600,7 +34604,7 @@
         <v>45184</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34657,7 +34661,7 @@
         <v>45852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34714,7 +34718,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34776,7 +34780,7 @@
         <v>45890</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34833,7 +34837,7 @@
         <v>45890</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34890,7 +34894,7 @@
         <v>45890</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34947,7 +34951,7 @@
         <v>45891.58381944444</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35009,7 +35013,7 @@
         <v>45852</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35066,7 +35070,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35128,7 +35132,7 @@
         <v>45852</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35185,7 +35189,7 @@
         <v>45852</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35242,7 +35246,7 @@
         <v>45845</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35299,7 +35303,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35356,7 +35360,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35413,7 +35417,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35470,7 +35474,7 @@
         <v>45204</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35527,7 +35531,7 @@
         <v>45852</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35584,7 +35588,7 @@
         <v>45852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35641,7 +35645,7 @@
         <v>44099</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35698,7 +35702,7 @@
         <v>44795</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35755,7 +35759,7 @@
         <v>45891</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35817,7 +35821,7 @@
         <v>45328</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35874,7 +35878,7 @@
         <v>45229</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35936,7 +35940,7 @@
         <v>44781</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35998,7 +36002,7 @@
         <v>44781</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36060,7 +36064,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36117,7 +36121,7 @@
         <v>45147</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36179,7 +36183,7 @@
         <v>44831</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36236,7 +36240,7 @@
         <v>45898.42240740741</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36298,7 +36302,7 @@
         <v>45189</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36355,7 +36359,7 @@
         <v>45547</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36412,7 +36416,7 @@
         <v>44082</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36469,7 +36473,7 @@
         <v>45328.47</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36531,7 +36535,7 @@
         <v>45167</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36593,7 +36597,7 @@
         <v>45026</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36650,7 +36654,7 @@
         <v>44159</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36707,7 +36711,7 @@
         <v>44817</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36769,7 +36773,7 @@
         <v>45478</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36826,7 +36830,7 @@
         <v>44085</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36883,7 +36887,7 @@
         <v>44442</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36940,7 +36944,7 @@
         <v>45226</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36997,7 +37001,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37054,7 +37058,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37111,7 +37115,7 @@
         <v>45688</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37168,7 +37172,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37225,7 +37229,7 @@
         <v>44075</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37282,7 +37286,7 @@
         <v>45477</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37339,7 +37343,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37396,7 +37400,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37458,7 +37462,7 @@
         <v>45182</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37520,7 +37524,7 @@
         <v>44776</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37577,7 +37581,7 @@
         <v>44840</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37634,7 +37638,7 @@
         <v>44231</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37691,7 +37695,7 @@
         <v>44103</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37753,7 +37757,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37810,7 +37814,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37867,7 +37871,7 @@
         <v>44232</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37924,7 +37928,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37981,7 +37985,7 @@
         <v>44449</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38038,7 +38042,7 @@
         <v>44844</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38095,7 +38099,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38152,7 +38156,7 @@
         <v>44823</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38209,7 +38213,7 @@
         <v>44859</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38266,7 +38270,7 @@
         <v>44386</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38328,7 +38332,7 @@
         <v>44862</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38385,7 +38389,7 @@
         <v>44074</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38442,7 +38446,7 @@
         <v>44602</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38499,7 +38503,7 @@
         <v>45016</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38556,7 +38560,7 @@
         <v>45110</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38613,7 +38617,7 @@
         <v>44411</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38670,7 +38674,7 @@
         <v>44212</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38727,7 +38731,7 @@
         <v>44250</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38784,7 +38788,7 @@
         <v>44895</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38841,7 +38845,7 @@
         <v>45209</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38898,7 +38902,7 @@
         <v>44466</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38955,7 +38959,7 @@
         <v>45107</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39017,7 +39021,7 @@
         <v>44173</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39074,7 +39078,7 @@
         <v>44909</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39136,7 +39140,7 @@
         <v>45050</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39198,7 +39202,7 @@
         <v>44160</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39255,7 +39259,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39312,7 +39316,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39369,7 +39373,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39426,7 +39430,7 @@
         <v>44862</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39483,7 +39487,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39540,7 +39544,7 @@
         <v>44130</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39597,7 +39601,7 @@
         <v>44142</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39654,7 +39658,7 @@
         <v>44963</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39711,7 +39715,7 @@
         <v>44942</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39768,7 +39772,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39825,7 +39829,7 @@
         <v>44922</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39887,7 +39891,7 @@
         <v>45211</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39944,7 +39948,7 @@
         <v>45057</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40025,7 +40029,7 @@
         <v>44433</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40087,7 +40091,7 @@
         <v>45231</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40144,7 +40148,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40201,7 +40205,7 @@
         <v>44790</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40258,7 +40262,7 @@
         <v>45386</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40315,7 +40319,7 @@
         <v>44905</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40372,7 +40376,7 @@
         <v>44852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40429,7 +40433,7 @@
         <v>45076</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40486,7 +40490,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40543,7 +40547,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40600,7 +40604,7 @@
         <v>44694</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40657,7 +40661,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40714,7 +40718,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40771,7 +40775,7 @@
         <v>44140</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40828,7 +40832,7 @@
         <v>45111</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40885,7 +40889,7 @@
         <v>44964</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40942,7 +40946,7 @@
         <v>44480</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40999,7 +41003,7 @@
         <v>44440</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41061,7 +41065,7 @@
         <v>44110</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41118,7 +41122,7 @@
         <v>44995</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41180,7 +41184,7 @@
         <v>44602</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41237,7 +41241,7 @@
         <v>44865</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41294,7 +41298,7 @@
         <v>45366</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41351,7 +41355,7 @@
         <v>45006</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41408,7 +41412,7 @@
         <v>44155</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41465,7 +41469,7 @@
         <v>44467</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41522,7 +41526,7 @@
         <v>44140</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41579,7 +41583,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41636,7 +41640,7 @@
         <v>45075</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41693,7 +41697,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41750,7 +41754,7 @@
         <v>44147</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41807,7 +41811,7 @@
         <v>44816</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41864,7 +41868,7 @@
         <v>44848</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41921,7 +41925,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41978,7 +41982,7 @@
         <v>44887</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42035,7 +42039,7 @@
         <v>45245</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42097,7 +42101,7 @@
         <v>44483</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42154,7 +42158,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42211,7 +42215,7 @@
         <v>45231</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42268,7 +42272,7 @@
         <v>44708</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42325,7 +42329,7 @@
         <v>45222</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42382,7 +42386,7 @@
         <v>45229</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42444,7 +42448,7 @@
         <v>45075</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42501,7 +42505,7 @@
         <v>45547</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42558,7 +42562,7 @@
         <v>44169</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42620,7 +42624,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42677,7 +42681,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42734,7 +42738,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42791,7 +42795,7 @@
         <v>44957</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42853,7 +42857,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42915,7 +42919,7 @@
         <v>44694</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42972,7 +42976,7 @@
         <v>45733</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43029,7 +43033,7 @@
         <v>45268</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43086,7 +43090,7 @@
         <v>45168</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43143,7 +43147,7 @@
         <v>45071</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43200,7 +43204,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43257,7 +43261,7 @@
         <v>44978</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43314,7 +43318,7 @@
         <v>44858</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43371,7 +43375,7 @@
         <v>44467</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43428,7 +43432,7 @@
         <v>45509</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43490,7 +43494,7 @@
         <v>45386</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43547,7 +43551,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43604,7 +43608,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43661,7 +43665,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43718,7 +43722,7 @@
         <v>44977</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43780,7 +43784,7 @@
         <v>44603</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43837,7 +43841,7 @@
         <v>44784</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43894,7 +43898,7 @@
         <v>44603</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43951,7 +43955,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44008,7 +44012,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44070,7 +44074,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44127,7 +44131,7 @@
         <v>45019</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44189,7 +44193,7 @@
         <v>44871</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44246,7 +44250,7 @@
         <v>45160</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44308,7 +44312,7 @@
         <v>44977</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44370,7 +44374,7 @@
         <v>45516</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44427,7 +44431,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44484,7 +44488,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44541,7 +44545,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44598,7 +44602,7 @@
         <v>45016</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44660,7 +44664,7 @@
         <v>45191</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44717,7 +44721,7 @@
         <v>45677</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44774,7 +44778,7 @@
         <v>45214</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44831,7 +44835,7 @@
         <v>45033</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44888,7 +44892,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44945,7 +44949,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45002,7 +45006,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45059,7 +45063,7 @@
         <v>44985</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45121,7 +45125,7 @@
         <v>44974</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45183,7 +45187,7 @@
         <v>44945</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45240,7 +45244,7 @@
         <v>45154</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45297,7 +45301,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45354,7 +45358,7 @@
         <v>45205</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45411,7 +45415,7 @@
         <v>44886</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45468,7 +45472,7 @@
         <v>45667</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45525,7 +45529,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45582,7 +45586,7 @@
         <v>45457</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45639,7 +45643,7 @@
         <v>44977</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45701,7 +45705,7 @@
         <v>44855</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45763,7 +45767,7 @@
         <v>44934</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45820,7 +45824,7 @@
         <v>44809</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45877,7 +45881,7 @@
         <v>44825</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45934,7 +45938,7 @@
         <v>45281</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45996,7 +46000,7 @@
         <v>45214</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46053,7 +46057,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46110,7 +46114,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46167,7 +46171,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46224,7 +46228,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46281,7 +46285,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46338,7 +46342,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46395,7 +46399,7 @@
         <v>45098</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46452,7 +46456,7 @@
         <v>44957</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46514,7 +46518,7 @@
         <v>44957</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46576,7 +46580,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46633,7 +46637,7 @@
         <v>45697</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46690,7 +46694,7 @@
         <v>45692</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46752,7 +46756,7 @@
         <v>45001</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46809,7 +46813,7 @@
         <v>45001</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46866,7 +46870,7 @@
         <v>45601</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46923,7 +46927,7 @@
         <v>45345</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46980,7 +46984,7 @@
         <v>45013</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47042,7 +47046,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>44434</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>44995</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44876</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45057</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44223</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44238</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>44473</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>45062</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44972</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45649</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44169</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45099</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45013</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45799</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45666</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45014</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>44536</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44809</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44512</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44602</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44546</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44733</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44839</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44889</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45814</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45231</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>44671</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45077</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45229</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44483</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45183</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45184</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44995</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44099</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45133</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>44803</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44599</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>44831</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>44995</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44749</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44393</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>44419</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44299</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44299</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44824</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44853</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44430</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44546</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>44553</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44519</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44323</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44090</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44166</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44265</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44423</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44407</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44512</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44266</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44266</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44468</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>44476</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44536</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44599</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44628</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>44824</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>44467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>44602</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44536</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44719</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44391</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44417</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44466</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44496</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>44480</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44719</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44370</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44585</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44102</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>44725</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44619</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44251</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>44468</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44168</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44426</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>44581</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44256</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44169</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44266</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44265</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>44299</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>44712</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44783</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>44783</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>44449</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>44783</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>44130</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>44130</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44510</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>44351</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>44264</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44099</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>44495</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>44701</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>44683</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>44550</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44475</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44182</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44182</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44415</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44571</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44085</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>44455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>44455</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>44455</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44601</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>44602</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44706</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44837</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44838</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>44607</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44480</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44260</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44797</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44725</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44411</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44526</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44616</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44369</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44832</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>44522</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44531</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44840</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44581</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44238</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44789</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44467</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44523</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44827</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44375</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44169</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>44141</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44270</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>44266</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>44463</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44512</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44762</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44225</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44605</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>44790</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44473</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44539</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44439</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>44393</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44768</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44824</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44641</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45678</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45070</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>44859</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44859</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>45215</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44847</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44696</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44797</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44242</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44166</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45107</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45697</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45697</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>45677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>44434</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45177</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>44488</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>45595</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44789</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45694</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45188</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44319</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45414</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>45142</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45362</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>44837</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44551</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>44888</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44945</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44875</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45230</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45547</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45393</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>44992</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>44888</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>44888</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>44412</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45666</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45329</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45208</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45100</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>44952</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>44362</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45322</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>44628</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45698</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45180</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45457</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45106</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>44830</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45002</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>44601</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45097</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>45019</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>44335</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45463</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45517</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44789</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44474</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44789</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45120</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44844</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45415</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45393</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45076</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>44461</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>44089</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45785</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44460</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45322</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45281</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45152</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>44495</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>45148</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44833</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45785</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45281</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45478</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45461</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45786</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>44130</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45462</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45461</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45099</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45105</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44621</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45174</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>44406</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>44886</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>45328</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45328</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>45481</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45328</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>44523</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45483</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>44860</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45470</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45153</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44838</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45461</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>44483</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45479</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>45239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>45169</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>44151</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45478</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45475</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>44964</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45125</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45108</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45674</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>44840</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>44858</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45438</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44596</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>44970</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45672</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45798.5558912037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>44582</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45475</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44099</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45240</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>44551</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>44551</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>44602</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>44139</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>44602</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45560</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45393</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45483</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>44112</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>44089</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45518</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>45231</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45799</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45362</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45211</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45460</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45362</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44491</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45517</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45393</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>45393</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44994</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45810</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>44173</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>44985</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44130</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44130</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45348</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45348</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44140</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45077</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44151</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>45165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45344</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44146</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45050</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44889</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45813</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45813</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45225</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45531</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45692</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>44957</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45636</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44638</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>45674</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>44817</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45141</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45141</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45547</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>44699</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45215</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>45215</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45822</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>44195</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45196</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45845</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44158</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44980</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44659</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44995</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>44678</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>44238</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>44172</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>45827</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45827</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44623</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>45870</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45827</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45827</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>45384</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44964</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44602</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45194</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45590</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45238</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44445</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45833</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>44664</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45247</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>44266</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>44600</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>44712</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45096</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45223</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45833</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45169</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45204</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45153</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45762</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45316</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>44797</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45565</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44212</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45604</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45204</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45758</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45758</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>44760</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>45163</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>44643</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45477</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>44461</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45230</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32180,7 +32180,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45061</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>45001</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>45001</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45842</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45842</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>44968</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>45594</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45001</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44987</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>44518</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44851</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45700</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>45302</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45322</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44895</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45096</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33506,7 +33506,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>45666</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>44964</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45885</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>45268</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>44439</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>44965</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>44519</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>45352</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>45041</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45006</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>45852</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>45853</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>44886</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>44888</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45184</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45890</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45890</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45890</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45891.58381944444</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45852</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>45852</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45852</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45845</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45204</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45852</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44099</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44795</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45891</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>45328</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>45229</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>44781</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44781</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45147</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44831</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>45898.42240740741</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45189</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>45547</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44082</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>45328.47</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>45167</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>45026</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44159</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44817</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>45478</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44085</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>44442</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>45226</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>45688</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44075</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45477</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45182</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>44776</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>44840</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>44231</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>44103</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>44232</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>44449</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>44844</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44823</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44859</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44386</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>44862</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>44074</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>44602</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>45016</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45110</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>44411</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>44212</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38731,7 +38731,7 @@
         <v>44250</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>44895</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>45209</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>44466</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>45107</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>44173</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44909</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45050</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44160</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44862</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44130</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44142</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44963</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44942</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44922</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45211</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>45057</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44433</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>45231</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>44790</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>45386</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>44905</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>44852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>45076</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40490,7 +40490,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>44694</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44140</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>45111</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>44964</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>44480</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>44440</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44110</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>44995</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44602</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44865</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>45366</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45006</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>44155</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>44467</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>44140</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45075</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>44147</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>44816</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>44848</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>44887</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>45245</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>44483</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42215,7 +42215,7 @@
         <v>45231</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>44708</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>45222</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45229</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>45075</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>45547</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42562,7 +42562,7 @@
         <v>44169</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>44957</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>44694</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45733</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>45268</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         <v>45168</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45071</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44978</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43318,7 +43318,7 @@
         <v>44858</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>44467</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45509</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>45386</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>44977</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44603</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>44784</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>44603</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45019</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>44871</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>45160</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>44977</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45516</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>44908</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>45016</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45191</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>45677</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45214</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45033</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>44985</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>44974</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>44945</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45154</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45205</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>44886</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45472,7 +45472,7 @@
         <v>45667</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45529,7 +45529,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45586,7 +45586,7 @@
         <v>45457</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45643,7 +45643,7 @@
         <v>44977</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>44855</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>44934</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>44809</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>44825</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45281</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>45214</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45189</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45098</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>44957</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>44957</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>44965</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45697</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45692</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>45001</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45001</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45601</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45345</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>45013</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>44434</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>44995</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44876</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45057</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44223</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45062</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44238</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>45649</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44169</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44972</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>45666</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44809</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45099</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45014</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45799</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44481</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>44536</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>45013</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44512</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44602</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44546</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44733</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44839</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44671</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>45184</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>44749</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45183</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44831</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>44599</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45814</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44803</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>45229</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45903</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>45903.64179398148</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44995</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>45231</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44995</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44889</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45133</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45077</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44099</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>44483</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>44393</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44419</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44299</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>44299</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44824</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44430</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44853</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44473</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44546</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44553</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44519</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>44323</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44090</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44265</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44423</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>44166</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44407</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44512</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44266</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44266</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44476</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44628</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44599</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44824</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44467</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44602</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44536</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44719</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>44391</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44417</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>44466</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44496</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44480</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44719</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>44370</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44102</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44725</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>44251</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44619</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>44468</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44515</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44168</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44426</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44581</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44256</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44169</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44266</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44265</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>44299</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>44712</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44783</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>44783</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>44449</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>44351</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44783</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44130</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44510</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44264</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44099</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44495</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>44496</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>44683</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>44550</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>44701</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44475</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44412</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44426</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>44182</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>44182</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>44571</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>44415</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>44085</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>44455</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44601</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>44455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44455</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44607</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>44260</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44797</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44725</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44725</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>44411</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44526</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>44369</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>44616</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>44531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>44832</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>44522</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>44840</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>44581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>44789</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>44827</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>44467</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>44238</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>44523</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>44375</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44169</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44141</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44270</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44266</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>44512</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>44762</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44225</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44790</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44605</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44539</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44439</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>44463</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44473</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44824</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44474</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45483</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44393</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>44768</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44964</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45697</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45697</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>44641</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>44480</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45110</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>44784</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>44602</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>44362</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44706</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>44837</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>44838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44957</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45006</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45386</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>45120</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45674</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45478</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45547</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44825</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45666</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45111</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>44980</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>44412</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>44140</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>45698</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44789</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44789</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45604</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>44212</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>44461</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45547</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45182</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>44789</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45516</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45167</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>45165</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>45785</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45019</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45785</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>45457</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44840</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44823</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>44844</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>44790</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45362</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>44551</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44551</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45517</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45281</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45477</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44977</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>44440</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44110</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45461</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45517</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>44970</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>44909</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45016</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44858</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>44266</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44859</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45786</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>44335</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45565</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>44155</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>44433</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44781</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45762</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>45393</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44837</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45196</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45001</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>44621</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45345</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45189</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44859</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44151</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45013</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44847</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45222</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>44945</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>44483</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45672</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45461</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>44169</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45096</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45231</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44987</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45674</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45154</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45414</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45457</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45001</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44406</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45798.5558912037</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45231</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45560</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45019</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44862</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45002</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45393</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>44888</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45153</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44809</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45240</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45799</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45141</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45152</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45163</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>44871</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45475</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>44696</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>45247</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>44159</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>44887</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45463</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44831</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>44678</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>44830</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45810</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45208</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45362</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>44139</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45147</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45148</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44964</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44994</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44795</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45322</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>45096</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44968</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44817</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45758</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45245</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>44603</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45215</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45001</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45813</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45813</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45481</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45268</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45230</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44434</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45099</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45547</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>44922</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>44895</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45076</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45531</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>44638</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>44859</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>44112</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>44495</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45322</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45822</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45827</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45827</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45827</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45827</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>44587</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45870</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>45077</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45344</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45226</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>45833</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>44603</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45833</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45677</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>44945</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>44089</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45479</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45097</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45601</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>44797</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45842</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
         <v>45125</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45105</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45700</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45842</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45191</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>45733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45231</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45885</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44965</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44140</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45348</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45100</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45890</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45890</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45890</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45891.58381944444</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45852</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>45852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>45852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45852</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>45891</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>45845</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>45853</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44852</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44888</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45898.42240740741</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>44957</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45901.49755787037</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>45901</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>45902.32601851852</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>44085</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31304,7 +31304,7 @@
         <v>45845</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>44797</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>45050</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45901</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45692</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45509</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44838</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45214</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>45901</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45905.46659722222</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31889,7 +31889,7 @@
         <v>44694</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>44082</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>44964</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>44601</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45328</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>44952</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>44089</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45076</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45075</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45209</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45214</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45169</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>44862</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45098</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44664</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44848</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45281</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45281</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45362</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44130</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45168</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45677</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>44523</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33490,7 +33490,7 @@
         <v>45107</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>44602</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>45483</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44602</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44995</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>44760</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>44099</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45026</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>44708</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>45180</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34536,7 +34536,7 @@
         <v>45547</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>44602</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>44466</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45470</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45666</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>45352</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45393</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>45393</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45075</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>45194</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>44386</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>45215</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45215</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>45107</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44480</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>45268</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44860</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45211</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>45106</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44889</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44844</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>44817</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45590</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45678</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>44853</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>45041</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44886</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45211</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>45460</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>45142</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44232</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>44776</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45230</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>44875</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45204</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>44238</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>45316</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>44712</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>45230</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45098</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45302</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44491</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45223</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45475</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>44151</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>44833</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45225</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>44855</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>44985</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>44805</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45694</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>45322</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>44103</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45033</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44908</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44985</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>45697</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>44888</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>44888</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>44623</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>45070</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44449</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44551</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>45478</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45478</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45595</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45174</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44467</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45688</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45177</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45366</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44166</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>45477</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44659</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39994,7 +39994,7 @@
         <v>44160</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>44602</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>44602</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>44816</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>44519</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44596</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45238</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>44442</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45692</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>45214</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>45189</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>44140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40802,7 +40802,7 @@
         <v>45061</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>44130</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>45001</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>45001</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41030,7 +41030,7 @@
         <v>44130</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>44600</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41144,7 +41144,7 @@
         <v>44957</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>45229</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>44439</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>44099</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>45438</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45016</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>45229</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>45328</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>44886</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>44158</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45188</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42267,7 +42267,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>44142</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45006</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>44643</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>44319</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45348</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45108</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45328</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45328</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>44858</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>44781</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>44905</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44957</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44934</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>44628</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>44851</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>44147</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>44242</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45384</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>44195</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>45204</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>45667</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>44173</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>44977</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>44977</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>44445</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45415</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>44483</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45141</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45184</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>44411</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>44995</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>44964</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>44460</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>44461</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>44212</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>45071</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>45594</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>44963</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44996,7 +44996,7 @@
         <v>44978</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>44886</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>44992</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>45153</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45329</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>44173</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>44963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>44965</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45581,7 +45581,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45643,7 +45643,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>44699</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45160</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>44694</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>44582</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45393</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>44840</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46223,7 +46223,7 @@
         <v>44250</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>44895</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>44172</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45205</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>44146</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45386</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46627,7 +46627,7 @@
         <v>45462</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>45328.47</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46746,7 +46746,7 @@
         <v>44231</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>45050</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>45636</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>44942</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>45239</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>45758</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>44488</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>44467</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>45057</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>44434</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>44995</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44876</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45057</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44223</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44238</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>44473</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>45062</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44972</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45649</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44169</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45099</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45013</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45799</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45666</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45014</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>44536</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44809</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44512</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44602</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44546</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44733</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44839</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44889</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45231</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45814</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>44671</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45229</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45077</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44483</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45183</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45184</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45133</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>44803</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>44995</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44099</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45903.64179398148</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44599</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45903</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>44831</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44995</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>44749</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>44393</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44419</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44299</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>44299</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44824</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44430</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44853</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44473</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44546</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44553</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44519</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>44323</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44090</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44166</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44223</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44265</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44423</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44407</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44512</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44266</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44266</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44476</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44628</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44599</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44824</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44467</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44602</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44719</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44536</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>44391</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44417</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>44466</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44480</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44496</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44719</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44370</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>44585</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44102</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44725</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>44468</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44619</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>44251</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>44515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44168</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44426</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44581</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44256</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44169</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44266</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44265</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>44299</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>44712</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44783</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>44783</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>44449</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>44351</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44510</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44783</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44130</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44130</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44264</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44099</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44495</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>44496</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>44701</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>44683</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44475</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44550</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44412</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44426</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>44182</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>44182</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>44415</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>44455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>44571</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44601</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44455</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>44455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44602</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>44706</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44837</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44838</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44607</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44480</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44260</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44797</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44616</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44832</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44725</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44522</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44369</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44840</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44725</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44411</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>44526</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>44523</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>44531</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>44375</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44581</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44141</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44789</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44827</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>44467</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44725</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44169</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>44270</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44266</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44512</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44762</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44790</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>44539</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44439</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44225</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44463</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44824</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44488</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>44789</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44319</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44238</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>44393</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>44768</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>45678</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>44859</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45215</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44847</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45414</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44242</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45362</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44837</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45697</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45697</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45177</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>44888</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45070</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>44859</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44696</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45230</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45677</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44888</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44166</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45107</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45595</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45694</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45188</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45142</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44551</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45208</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44945</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44875</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45393</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45100</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44952</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44992</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45547</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44412</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45666</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45329</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45457</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44362</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45322</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45106</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44830</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44628</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45180</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45698</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45002</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>44805</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>44601</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45097</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45019</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44789</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>44474</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44789</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45463</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45393</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45120</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45076</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>44335</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>44844</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44089</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45415</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45517</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45152</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>44461</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45148</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>44460</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45478</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45785</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45322</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45281</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>44495</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44833</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45785</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>45281</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45105</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>44621</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45174</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45461</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45786</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45328</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45328</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45481</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45462</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>44605</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>44130</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45099</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45328</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>44406</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>44886</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44473</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45153</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>44523</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45479</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45483</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44860</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45470</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>44838</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>44483</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>44964</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45125</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45108</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>45461</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>45239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45169</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45438</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>44596</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>44151</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45478</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45475</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>44582</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>44840</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44858</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>44551</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44551</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44139</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>44970</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45672</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45674</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45475</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>44099</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45211</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>45517</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45240</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>44602</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>44602</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>44641</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45393</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45483</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45230</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44112</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45560</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>44089</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45518</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>44140</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>45077</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45231</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>45799</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45362</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>44151</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45460</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>45362</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45165</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45344</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44491</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45393</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45393</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>44994</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44173</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44985</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>44130</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>44130</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45214</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45050</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45225</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45348</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45348</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>44963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45692</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45674</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45141</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45141</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>44146</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>44699</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45215</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45215</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>44587</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>44889</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45196</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45813</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>45813</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>44957</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45636</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45531</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45547</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>44638</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>45194</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>44195</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45822</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44664</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44158</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>44712</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44980</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45096</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44659</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44995</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>44238</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>45827</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45169</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>45204</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44172</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45827</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>45153</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>45827</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>45827</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44623</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45384</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44964</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44212</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44602</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>45758</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45758</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44760</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45833</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45590</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45833</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44445</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45163</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45247</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44266</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44600</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44853</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>45223</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45477</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45762</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44518</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>44851</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>45316</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44797</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45565</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45604</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45302</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45322</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44895</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45204</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>44643</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>44461</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45230</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45061</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45001</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45001</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>45268</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44968</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>45594</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45001</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44987</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44439</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44965</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44519</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45096</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45666</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>44964</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45352</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>45041</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45006</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44886</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44888</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45204</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>45184</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44795</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44781</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44781</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>45147</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44099</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45189</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>45328</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>45229</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44817</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44442</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45226</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45688</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45098</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45477</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>45182</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44840</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44231</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44831</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44844</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44823</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44859</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44386</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44862</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>45842</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>45110</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44895</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45209</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44466</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>45842</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44909</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45050</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>45547</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>44862</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>44963</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45328.47</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45211</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45057</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45167</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>44433</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45231</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45026</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45076</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>44159</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45478</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>44480</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>44440</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>44110</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>44865</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45366</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45700</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>44155</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>44467</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>44140</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>44776</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45075</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>44147</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44103</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44848</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44887</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>44483</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45231</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>44232</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45229</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45885</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>44449</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>44602</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45016</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44411</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>44212</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>44250</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45733</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45107</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>44173</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45852</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>45853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>44160</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45890</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45890</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>45890</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45891.58381944444</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45852</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45852</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45845</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45852</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>44130</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45891</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>44142</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>44942</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45898.42240740741</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44922</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>44790</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45386</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>44905</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44694</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44140</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45111</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>44964</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>44602</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45902.32601851852</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45901</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45845</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45901.49755787037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45006</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>44816</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45245</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45901</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45908.35550925926</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45905.46659722222</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>44708</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45222</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45075</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>45907</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>45547</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>44434</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44169</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45901</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>44957</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>44694</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45268</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45168</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45071</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>44978</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>44858</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45870</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45810</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>44467</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45509</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45902</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45386</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>44977</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>44603</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>44784</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>44603</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>45019</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>44871</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45160</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>44977</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45516</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>44908</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45016</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>45191</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45677</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>45214</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>45033</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>44985</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>44974</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>44945</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>45154</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45205</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>44886</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>45667</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>45457</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>44977</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>44855</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>44934</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>44809</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>44825</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45281</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45214</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45189</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45098</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>44957</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>44957</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>44965</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45697</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45692</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45001</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45001</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>45601</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45345</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>45013</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>44434</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>44995</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44876</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45057</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>44223</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44238</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>44473</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>45062</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44972</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45649</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44169</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45099</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45013</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45799</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45666</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45014</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>44536</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44809</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44512</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44602</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44546</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44733</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44839</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44889</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45231</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45814</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>44671</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45229</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45077</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44483</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45183</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45184</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45133</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>44803</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>44995</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44099</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45903.64179398148</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44599</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45903</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>44831</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44995</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>44749</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>44393</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44419</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44299</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>44299</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44824</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44430</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44853</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44473</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44546</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44553</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44519</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>44323</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44090</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44166</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44223</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44265</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>44423</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44407</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44512</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44266</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44266</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44476</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44628</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44599</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44824</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44467</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44602</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44719</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44536</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>44391</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44417</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>44466</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44480</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44496</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44719</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44370</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>44585</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44102</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44725</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>44468</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44619</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>44251</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>44515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44168</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44426</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44581</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44256</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>44169</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44266</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44265</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>44299</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>44712</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44783</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>44783</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>44449</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>44351</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44510</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44783</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44130</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44130</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44264</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44099</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44495</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>44496</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>44701</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>44683</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44475</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44550</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44412</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44426</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>44182</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>44182</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>44415</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>44455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>44571</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44601</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44455</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>44455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44602</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>44706</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44837</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44838</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44607</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44480</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44260</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44797</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44616</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44832</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44725</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44522</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44369</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44840</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44725</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44411</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>44526</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>44523</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>44531</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>44375</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44581</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44141</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44789</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44827</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>44467</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44725</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44169</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>44270</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44266</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44512</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44762</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44790</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>44539</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44439</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44225</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44463</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44824</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44488</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>44789</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44319</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44238</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>44393</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>44768</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>45678</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>44859</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45215</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44847</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45414</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44242</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45362</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44837</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45697</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45697</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45177</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>44888</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45070</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>44859</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44696</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45230</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45677</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44888</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>44888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44166</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45107</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45595</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45694</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45188</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45142</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44551</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45208</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44945</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44875</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45393</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45100</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44952</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44992</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45547</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44412</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45666</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45329</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45457</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44362</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45322</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45106</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44830</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44628</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45180</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45698</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45002</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>44805</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>44601</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45097</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45019</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44789</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>44474</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44789</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45463</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45393</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45120</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45076</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>44335</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>44844</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44089</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45415</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45517</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45152</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>44461</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45148</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>44460</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45478</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45785</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45322</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45281</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>44495</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44833</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45785</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>45281</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45105</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>44621</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45174</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45461</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45786</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45328</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45328</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45481</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45462</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>44605</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>44130</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45099</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45328</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>44406</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>44886</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44473</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45153</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>44523</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45479</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45483</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44860</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45470</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>44838</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>44483</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>44964</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45125</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45108</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>45461</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>45239</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45169</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45438</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>44596</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>44151</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45478</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45475</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>44582</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>44840</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44858</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>44551</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44551</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44139</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>44970</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45672</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45674</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45475</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>44099</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45211</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>45517</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45240</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>44602</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>44602</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>44641</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45393</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45483</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45230</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44112</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45560</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>44089</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45518</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>44140</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>45077</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45231</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>45799</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45362</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>44151</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45460</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>45362</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45165</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45344</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44491</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45393</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45393</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>44994</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44173</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44985</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>44130</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>44130</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45214</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45050</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45225</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45348</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45348</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>44963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45692</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45674</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45141</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45141</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>44146</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>44699</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45215</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45215</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>44587</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>44889</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45196</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>44678</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45813</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>45813</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>44957</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45636</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45531</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45547</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>44638</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>45194</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>44195</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45822</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44664</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44158</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>44712</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44980</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45096</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44659</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44995</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>44238</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>45827</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45169</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>45204</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44172</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45827</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>45153</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>45827</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>45827</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44623</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45384</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44964</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44212</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44602</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>45758</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45758</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44760</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45833</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45590</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45833</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44445</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45163</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>45772.63049768518</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45247</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44266</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44600</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44853</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>45223</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45477</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45762</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44518</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>44851</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>45316</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44797</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45565</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45604</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45302</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45322</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44895</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45204</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>44643</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>44461</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45230</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45061</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45001</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45001</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>45268</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44968</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>45594</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45001</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44987</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44439</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44965</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44519</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45096</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45666</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>44964</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45352</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>45041</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45006</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44886</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44888</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45204</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>45184</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>44795</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44781</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44781</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>45147</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44099</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45189</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>45328</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>45229</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44817</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44442</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45226</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45688</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45098</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45477</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>45182</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44840</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44231</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>45594.65637731482</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44831</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44844</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44823</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44859</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44386</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44862</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>45842</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>45110</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44895</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45209</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44466</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>45842</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44909</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45050</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>45547</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>44862</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>44963</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45328.47</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45211</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45057</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45167</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>44433</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45231</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45026</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45076</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>44159</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45478</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>44480</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>44440</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>44110</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>44865</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45366</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45700</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>44155</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>44467</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>44140</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>44776</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45075</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>44147</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44103</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44848</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44887</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>44483</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45231</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>44232</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45229</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45885</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>44449</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>44602</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45016</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44411</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>44212</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>44250</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45733</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45107</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>44173</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45852</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>45853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>44160</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45890</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45890</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>45890</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45891.58381944444</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45852</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45852</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45845</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45852</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>44130</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45891</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>44142</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>44942</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45898.42240740741</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44922</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>44790</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45386</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>44905</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44694</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44140</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45111</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>44964</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>44602</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45902.32601851852</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45901</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45845</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45901.49755787037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45006</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>44816</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45245</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45901</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45908.35550925926</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45905.46659722222</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>44708</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45222</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45075</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>45907</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>45547</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>44434</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44169</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45901</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>44957</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>44694</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45268</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45168</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45071</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>44978</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>44858</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45870</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45810</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>44467</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45509</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45902</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45386</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>44977</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>44603</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>44784</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>44603</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>45019</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>44871</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45160</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>44977</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45516</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>44908</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45016</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>45191</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45677</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>45214</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>45033</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>44985</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>44974</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>44945</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>45154</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45205</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>44886</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>45667</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>45457</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>44977</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>44855</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>44934</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>44809</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>44825</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45281</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45214</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45189</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45098</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>44957</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>44957</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>44965</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45697</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45692</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45001</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45001</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>45601</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45345</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>45013</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>44434</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>44995</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44876</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45057</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44223</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45062</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44238</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45225</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>44223</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>45649</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>44972</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44169</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>44168</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44500</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45666</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45099</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45014</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>44809</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45799</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44481</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>44536</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>45013</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44512</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44602</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44546</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44733</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44839</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>45183</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44749</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44831</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>44599</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>45814</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>44671</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45184</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44803</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>45229</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>44995</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45231</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>44995</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44889</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45133</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>45077</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45903</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44483</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45903</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>44393</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44419</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44299</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>44299</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44824</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44430</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44853</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>44473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44553</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44546</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>44519</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44323</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44166</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44223</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>44265</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44423</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44407</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44512</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44266</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44266</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44468</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44476</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44599</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44628</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44824</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44602</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44536</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44719</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44391</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44417</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44466</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44496</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44480</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>44719</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44585</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44370</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44102</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44725</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44468</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>44619</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>44515</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44168</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>44251</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44426</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44581</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44256</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44169</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44266</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>44265</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44299</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>44712</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44783</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44783</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44449</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44351</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44783</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44130</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44130</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44510</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44264</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44495</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>44496</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44701</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>44683</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44550</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>44412</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>44475</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44426</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44182</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44182</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>44415</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44571</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44601</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44455</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44455</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>44706</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44837</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44838</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44607</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>44260</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>44797</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>44725</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>44411</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44526</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11747,7 +11747,7 @@
         <v>44725</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44369</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>44531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44480</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>44581</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44238</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44789</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44827</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>44467</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>44169</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44463</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>44605</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>44473</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>44393</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>44768</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>44225</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44641</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45362</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45517</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45674</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>44616</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44362</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45547</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44832</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>44957</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>44825</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44858</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>45386</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>45666</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>45120</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44522</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45478</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44474</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45483</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44412</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>44964</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44980</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>45697</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45697</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44140</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>45698</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44789</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44789</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45604</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45110</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44212</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44461</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44784</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45547</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44840</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45182</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44789</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>45006</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45785</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44551</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44551</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45281</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>45477</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>44977</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>44110</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44523</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44970</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>44909</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45461</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45516</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>44266</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>44859</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45167</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45565</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44433</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44781</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45517</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>44375</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45019</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>44840</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44837</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45196</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>44621</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>44844</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45786</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44335</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>45189</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44130</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44141</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>44725</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>44440</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>44859</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45016</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45013</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>44155</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>44270</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44266</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45762</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>44483</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>44512</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44762</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45393</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45001</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45096</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>45231</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44987</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45345</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45154</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>44790</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45461</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>44539</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>44439</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>45457</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>44518</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>44862</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45002</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45393</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45153</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45163</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45674</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>44151</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44824</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>44847</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>44871</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45222</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45475</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44945</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44696</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45247</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>45672</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>44169</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45231</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45560</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45463</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45414</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45240</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>45799</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>44830</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45148</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45001</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44406</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45019</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44888</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44809</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44865</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45141</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45152</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45096</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44968</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>44887</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44817</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44831</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>44603</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>44678</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45208</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45362</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>45001</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>44139</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45147</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45813</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45813</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45481</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45268</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45230</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45547</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44922</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44964</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44994</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44795</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45322</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45076</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>45531</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45758</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44638</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>45245</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45111</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45165</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45099</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44112</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45457</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44823</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44495</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44895</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44790</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>45322</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45677</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44945</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45125</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45105</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45191</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44859</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45231</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45077</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45344</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45226</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>44603</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>45348</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45479</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45097</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45601</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>44797</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>44888</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45733</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>44965</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>44140</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45100</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45050</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45509</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>44838</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45214</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>44852</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>44957</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44694</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>44797</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>44601</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>45692</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>44952</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45076</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45075</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>44964</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45328</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45518</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>45209</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>45822</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>45169</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45214</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>44862</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>45098</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>44848</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>44664</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45362</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45281</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>45281</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45168</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>44130</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45677</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>45107</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45483</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>44523</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>44602</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>44602</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>44995</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30168,7 +30168,7 @@
         <v>44760</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45026</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45547</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44602</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44466</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45352</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45393</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45393</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>45075</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>44708</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45180</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31137,7 +31137,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45194</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45470</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45666</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44386</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>45215</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45215</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45107</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44480</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45268</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>44860</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45211</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45106</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>44889</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>45827</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>45827</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45590</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45827</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44844</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44853</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>44817</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45041</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45827</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>45678</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>44886</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45211</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45460</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>44232</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>45142</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45230</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33415,7 +33415,7 @@
         <v>44776</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>44875</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>44238</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44712</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>45204</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45230</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>45316</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>44491</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>45223</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>45098</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34171,7 +34171,7 @@
         <v>45302</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>45475</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>44151</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45833</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>45833</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>44833</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45225</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>44855</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45322</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45033</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>44908</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>44985</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>44805</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45694</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>44103</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44551</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>44985</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>45478</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45595</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45842</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45697</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45700</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44888</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>44888</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>44623</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>45070</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>45842</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>44449</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45478</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45177</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45366</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>44166</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>44659</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>44602</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>44602</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>45174</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>44816</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>44519</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>44467</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45885</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>45688</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>45477</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44130</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>45890</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>45890</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>45890</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>44974</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37988,7 +37988,7 @@
         <v>44439</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>44160</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>45229</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45891.58381944444</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45852</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>45852</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45852</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44886</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45852</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>45852</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38801,7 +38801,7 @@
         <v>45852</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45852</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44596</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45006</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45238</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45891</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>44319</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45348</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>44442</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45845</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>45692</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45214</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45189</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45328</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45328</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>44140</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>45061</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>44858</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45001</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45001</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>44781</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>44130</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>44905</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>44628</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>44147</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>44600</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>44957</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>44242</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45229</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45901.49755787037</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45902.32601851852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45667</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45438</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45016</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44173</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45328</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>45845</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>44158</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>45188</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44977</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>44977</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41902,7 +41902,7 @@
         <v>45204</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>44445</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>45905.46659722222</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>44142</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>44643</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>45108</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>44957</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>44934</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45184</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>44851</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>45907</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>44212</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>44434</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42824,7 +42824,7 @@
         <v>45594</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45908.35550925926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42938,7 +42938,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>44886</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43052,7 +43052,7 @@
         <v>45901</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
         <v>44173</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45384</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>44195</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>44965</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45204</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>45902</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45160</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>44694</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45415</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>44483</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>45393</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>45141</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>44840</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
         <v>44895</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>44411</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>44172</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>44995</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45205</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45915.41148148148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44450,7 +44450,7 @@
         <v>44964</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>44460</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>44461</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45071</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44735,7 +44735,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>45870</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>44963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>44992</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>45215</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>44942</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>45169</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45153</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45329</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45810</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>44963</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45239</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>44699</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45901</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45758</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>44488</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>44582</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>44467</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>44250</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45057</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44146</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45386</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46318,7 +46318,7 @@
         <v>45462</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45328.47</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44231</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45050</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45636</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>45898</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>45925.38545138889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>45853</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>44995</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>44434</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44876</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45057</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44223</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44238</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45062</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44473</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44473</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>45225</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>44223</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>44169</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45649</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44972</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44168</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44481</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45099</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45013</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>45014</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44536</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44809</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45799</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45666</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44512</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44602</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44546</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44733</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>44839</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44995</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45077</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44889</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44483</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>45183</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45903</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44599</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45903</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>44831</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45184</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44671</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44995</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44995</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>44749</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45133</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>44803</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45814</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45231</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45229</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44393</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44419</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>44299</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>44299</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44824</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44853</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44430</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44473</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44546</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44553</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44519</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44323</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44166</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44265</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44223</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44423</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44407</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44512</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>44266</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>44266</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44476</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44824</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44628</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44599</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44467</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44602</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44719</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44536</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44391</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>44417</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44466</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44496</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44480</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44719</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44370</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44102</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44725</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44251</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44619</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44468</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>44314.33722222222</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44168</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44515</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44426</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44581</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44580.49780092593</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>44844.52039351852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>44498.53755787037</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44256</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>44169</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>44266</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44370.40364583334</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44265</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44299</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>44712</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>44783</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44783</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44449</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44351</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>44783</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44510</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44130</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44130</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44130.44101851852</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>44264</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44602.5965162037</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44445.58675925926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44495</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>44701</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44683</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44550</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44475</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>44412</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44426</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44182</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>44182</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>44383.23978009259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>44415</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>44571</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>44455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44416.40457175926</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44601</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44455</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44455</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44490.60873842592</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>44607</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>44871.69347222222</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44260</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44733.77543981482</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>44725</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>44238</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>44725</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44411</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44369</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44526</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44523</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44531</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44375</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44141</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44581</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44725</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44789</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44795.44392361111</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44496.58033564815</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44467</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44827</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44270</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44266</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>44512</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>44762</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44169</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44539</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>44605</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44439</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44473</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44824</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44463</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>44847</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44797</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44242</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45697</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45697</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45177</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44488</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44641</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>44848.42216435185</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44225</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44789</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44319</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44480</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44393</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44768</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45231.40846064815</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44803.47950231482</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>45678</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>44859</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>44602</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45414</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45775.52854166667</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44616</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>44872.60384259259</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44832</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>44706</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44837</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44522</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>44838</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45362</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44837</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44830.4649074074</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44830.46849537037</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>44840</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44888</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44872.57288194444</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45230</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44409.41428240741</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44409.40363425926</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>44797</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44888</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>44888</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45328</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45208</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44481.24327546296</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45100</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>44952</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45229</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45891.58381944444</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45852</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45852.70716435185</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>45852</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45852</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45845</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45852</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45852</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45239.54861111111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45457</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45891</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44985.46709490741</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44831</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45106</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44158</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>44830</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>44980</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>44659</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>44995</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>45547</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45594.63619212963</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45594.63828703704</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>44805</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45328.47</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44238</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>45167</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>45026</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>44159</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>44789</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44474</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44789</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44172</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45478</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44928.36578703704</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45120</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>44844</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>44886.65092592593</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45415</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>44623</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>45456.83059027778</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>44461</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45181.92876157408</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45181.95491898148</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>45902.32601851852</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45384</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>45901</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45845</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>44776</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>44460</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44964</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>44103</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45901.49755787037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>44984.41238425926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>44957.44885416667</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44602</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>45322</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45281</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44232</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>44449</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44495</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>44858.60809027778</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>44833</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>45281</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44602</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45016</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>45908.35550925926</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44411</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>45590</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44725.39371527778</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45905.46659722222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44445</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44212</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44250</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45907</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45272.55362268518</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>44434</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45478.40751157407</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>45462</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45107</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45247</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44266</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44173</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44160</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44691.52616898148</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44601.78850694445</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44549.74741898148</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44600</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45901</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44530.82445601852</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44406</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>44886</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>44130</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>44523</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>45483</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>44142</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>44860</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45470</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>44838</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>44483</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>44942</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>44441.88092592593</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45223</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>44922</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45239</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>45169</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44790</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45870</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45386</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45810</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>44905</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>44151</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45902</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>45478</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45475</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45473.88313657408</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45481.49899305555</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44840</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44858</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>45481.49289351852</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45002.42188657408</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44970</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45672</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>44694</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>45475</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45762</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>44691.54077546296</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45088.83840277778</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>44140</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45111</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44964</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44602</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45316</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>44797</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44995</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44602</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>44602</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44596.55368055555</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45393</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45483</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45565</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45006</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44701.44754629629</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>44701.4744212963</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45729.56836805555</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>44112</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45518</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>44130.46172453704</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45901</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45362</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>44816</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45915.41148148148</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>44978.52131944444</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45245</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45460</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45362</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45594.62556712963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45604</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>44708</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45222</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45204</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45215</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44643</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>44461</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45075</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>45875.3396412037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45230</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>44491</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>44169</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45593.60288194445</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>44616.69246527777</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>45393</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45393</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45012.66421296296</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>44994</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45088.83430555555</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45061</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>44173</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45001</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45001</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45000.36373842593</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>44968</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45594</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45001</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>44985</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>44987</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>44130</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44130</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>44957</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>44694</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>44599.61034722222</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45268</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>45357.45089120371</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45096</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45168</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45666</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45071</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>44964</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45646.42061342593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>44830.47399305556</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45566.82973379629</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45348</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45348</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>44978</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44858</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>45727.34248842593</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44467</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45509</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45386</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45881.40907407407</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44824.55655092592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44627.34033564815</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>44978.49685185185</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44978.5737037037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44977</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44603</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44146</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45041</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>45635.43770833333</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>44587</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>44889</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44784</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44603</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44607.35009259259</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45473.87645833333</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44502.36780092592</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44701.36431712963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>45204</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45019</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>44795</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>44871</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45160</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45357.37618055556</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44977</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>45516</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>44957</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>44781</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>44781</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44942.58850694444</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45147</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>44908</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45056.46821759259</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>45016</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>45189</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>45636</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>45191</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45677</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45214</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45033</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45547</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44817</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>44195</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44169</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>44442</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>45753.61614583333</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>45226</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45126.65491898148</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>45688</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45635.44527777778</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45098</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>44985</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45477</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>44502.35746527778</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45182.5793287037</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45182</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>44974</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>44945</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45898</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45154</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>44872.57752314815</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45853</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>44840</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45925.38545138889</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45205</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>44231</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45205.31987268518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>44140.69324074074</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44844</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44823</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44859</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>44386</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44862</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44886</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>45667</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45646.42608796297</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45110</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45457</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44977</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>44855</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44895</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44934</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44809</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>44825</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>45281</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>45209</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>44466</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44909</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45050</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>44862</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45214</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44830.38502314815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45316.49630787037</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>44582.40109953703</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33506,7 +33506,7 @@
         <v>45646.45950231481</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>44963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>44140.68782407408</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45189</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>45220.48068287037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45211</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>45057</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45098</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44957</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>44433</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45231</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45520.59179398148</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44957</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>44852</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44965</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45076</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45697</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>45692</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44559.57041666667</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45001</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>45001</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>44464.49756944444</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45345</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>44480</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44440</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44110</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45594.6605787037</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44865</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45366</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44155</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44467</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44140</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>45075</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>45677</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>45138.60248842592</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44147</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44848</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44887</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>45646.43950231482</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44945</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45350.32991898148</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>45547</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>44412</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45666</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>45698</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>44483</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>44932.74261574074</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45231</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45229</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>44335</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45517</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45450.38120370371</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45785</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45071.37393518518</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>45733</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45785</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45070</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>44859</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>44696</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>44507.56865740741</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45461</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45786</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45786.44217592593</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>44166</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45107</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44130</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45790.69971064815</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>45595</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45694</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45188</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>45142</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>44551</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44875</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45393</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>44992</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45327.35068287037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45329</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45461</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44362</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45322</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44628</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45180</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45002</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>44601</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45097</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45019</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>45463</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45674</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45446.56626157407</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45393</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45076</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45798.46452546296</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45798.57403935185</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45152</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45240</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45148</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>45646.45209490741</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45560</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45799.27168981481</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45231</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45799</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45804.37456018518</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45805.43341435185</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45805.43864583333</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45478</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45105</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>44621</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45174</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>45328</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>45328</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>45481</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>44985.47086805556</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45328</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>45813</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45813</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45533.54609953704</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45813.57603009259</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45798.56348379629</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45153</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45531</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45479</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>44638</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>45822</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>44964</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>45125</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45108</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45826.59151620371</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>44596.54990740741</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45438</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>44596</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>45826.63324074074</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>44582</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>45827</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45827.53319444445</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>45827</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45827</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>45827</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44551</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44551</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>44139</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>44609.53502314815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45211</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
         <v>45833</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>45338.34245370371</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>45517</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45833</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45833.45259259259</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>45632.46648148148</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>45230</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>45835.36697916667</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45840.45864583334</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>45840.47563657408</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>45840.47953703703</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>45840.46840277778</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>45840.46559027778</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>45840.50141203704</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>45841.59056712963</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>44140</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>45077</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45841.48686342593</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>45842</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>45842</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>45700</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45772.63453703704</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>44151</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45165</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43266,7 +43266,7 @@
         <v>45344</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>45885</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>45214</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45050</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>45225</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45852.70430555556</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>45852</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>45692</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>45852</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>45852.72320601852</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45674</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>45890</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45890</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45890</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>44817</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45141</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45141</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>44699</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>45215</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>45215</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45103.46788194445</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45090.55078703703</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>44678</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45446.56141203704</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44731,7 +44731,7 @@
         <v>45194</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45238</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>44664.55688657407</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>44664</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45124.55633101852</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45772.63540509259</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>44712</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45096</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45169</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45204</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45153</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>44793.50563657407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>44424.38577546296</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45472,7 +45472,7 @@
         <v>45460.66567129629</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45529,7 +45529,7 @@
         <v>44212</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45586,7 +45586,7 @@
         <v>44823.44353009259</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45643,7 +45643,7 @@
         <v>45758</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>45758</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
         <v>44760</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45163</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>45357.38601851852</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>44853</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45477</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>44518</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>44851</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>45302</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45322</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>44895</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>45477.64910879629</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45477.65216435185</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45268</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>44439</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>44965</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46627,7 +46627,7 @@
         <v>44519</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45352</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46746,7 +46746,7 @@
         <v>45006</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45264.64241898148</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>44886</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>44888</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>45184</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45357.44695601852</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>45357.44873842593</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>45405.48912037037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -567,7 +567,7 @@
         <v>45478</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>44817</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>44995</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>44434</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>45814</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44876</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45057</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>44223</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44238</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>45062</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>44473</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44473</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>45225</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>44223</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>44169</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45649</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44972</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44168</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44500</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44481</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45099</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45013</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>45014</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44536</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44809</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45799</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45666</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>45614.55686342593</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44512</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44602</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44546</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44733</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>44839</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44995</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45077</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44889</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44483</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>45183</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45903</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44599</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45903</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>44831</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45184</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44671</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44995</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44995</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>44749</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45133</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45573.77701388889</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>44803</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45786.62152777778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45814</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45231</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>45852.71136574074</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45229</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44393</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44419</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>44299</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>44299</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44824</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44853</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44430</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44473</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44546</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44553</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44519</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44323</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44166</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44265</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44299.40710648148</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44223</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44423</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44407</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44512</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>44266</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>44266</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44866.87912037037</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44536</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44476</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44824</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44628</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44599</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44467</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44602</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44811.61142361111</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44719</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44536</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44391</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>44417</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44466</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44496</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44480</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44719</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44370</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>44361.34458333333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44102</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44725</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44251</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44791.42287037037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44619</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44468</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>